--- a/Data/indus.xlsx
+++ b/Data/indus.xlsx
@@ -467,594 +467,594 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता का सर्वाधिक मान्यता प्राप्त काल है</t>
+          <t>सिंधु सभ्यता का पत्तननगर (बंदरगाह) कौन-सा था ?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2500 ई०पू०-1750 ई०पू०</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2800 ई०पू०-2000 ई०पू०</t>
+          <t>रोपड़</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3500 ई०पू०-1800 ई०पू०</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>निश्चित नहीं हो सका है</t>
+          <t>कालीबंगन</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>सिंधु घाटी की सभ्यता निम्नलिखित में से किस सभ्यता के समकालीन नहीं थी ?</t>
+          <t>निम्नलिखित पशुओं में से किस एक का हड़प्पा सभ्यता में पाई मुहरों और टेराकोटा कलाकृतियों में निरूपण / अंकन नहीं हुआ था ?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ग्रीक की सभ्यता</t>
+          <t>शेर</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>मेसोपोटामिया की सभ्यता</t>
+          <t>हाथी</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>चीन की सभ्यता</t>
+          <t>गैंडा</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>मिस्र की सभ्यता</t>
+          <t>बाघ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">	सिंधु घाटी की सभ्यता कहाँ तक विस्तृत थी?</t>
+          <t>किस सिंधुकालीन स्थल से एक ईट पर बिल्ली का पीछा करते हुए कुत्ते के पंजों के निशान मिले हैं ?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>पंजाब, राजस्थान, गुजरात, उत्तर प्रदेश, हरियाणा, सिंध और बलुचिस्तान</t>
+          <t>चन्हुदड़ो</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>जाब, राजस्थान, गुजरात, उड़ीसा और बंगाल</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>राजस्थान, बिहार, बंगाल और उड़ीसा</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>पंजाब, दिल्ली और जम्मू-कश्मीर</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>सिंधु घाटी की सभ्यता में घोड़े के अवशेष कहाँ मिले हैं ?</t>
+          <t>निम्नलिखित में से कौन मोहनजोदड़ो की सबसे बड़ी इमारत मानी जाती है?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>सुरकोटदा</t>
+          <t>विशाल अन्नागार / धान्यकोठार</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>वणावली</t>
+          <t>विशाल स्नानागार</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>सभा भवन</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>सिंधु घाटी स्थल कालीबंगन किस प्रदेश में है ?</t>
+          <t>हड़प्पा सभ्यता की खोज किस वर्ष में हुई थी ?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>राजस्थान में</t>
+          <t>1921 ई०</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>गुजरात में</t>
+          <t>1901 ई०</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>मध्य प्रदेश में</t>
+          <t>1942 ई०</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश में</t>
+          <t>1935 ई०</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>निम्नलिखित में से किस पदार्थ का उपयोग हड़प्पा काल की मुद्राओं के निर्माण में मुख्य रूप से किया गया था ?</t>
+          <t xml:space="preserve">	रंगपुर जहाँ हड़प्पा की समकालीन सभ्यता थी, है -</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>सेलखड़ी (steatite)</t>
+          <t>सौराष्ट्र में</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>कांसा</t>
+          <t>राजस्थान में</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ताँवा</t>
+          <t>उत्तर प्रदेश में</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>लोहा</t>
+          <t>पंजाब में</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा सभ्यता किस युग की थी ?</t>
+          <t>भारत में चाँदी की उपलब्धता के प्राचीनतम साक्ष्य मिलते हैं</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>कांस्य युग</t>
+          <t>हड़प्पा संस्कृति में</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>नवपाषाण युग</t>
+          <t>पश्चिमी भारत की ताम्रपाषाण संस्कृति में</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>पुरापाषाण युग</t>
+          <t>वैदिक संहिताओं में</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>लौह युग</t>
+          <t>चॉदी के आहत मुद्राओं में</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>सिंधु घाटी सभ्यता के लोगों का मुख्य व्यवसाय क्या था ?</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>व्यापार</t>
-        </is>
+          <t>निम्न में से कौन से लक्षण सभ्यता के लोगों का सही चित्रण करता हैं 1. उनके विशाल महल और मन्दिर होते थे 2. वे देवियों और देवताओं दोनों की पूजा करते थे l 3. वे युद्ध में घोड़ों द्वारा खींचे जानेवाले रथों का प्रयोग करते थे नीचे दिए गये कूट का प्रयोग कर सही कथन को चुनिए</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>पशुपालन</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>शिकार</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>कृषि</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता के निवासी थे</t>
+          <t xml:space="preserve">	निम्नलिखित में से कौन-सी फसल हड़प्पाकालीन लोगों द्वारा उत्पादित नहीं की जाती थी?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>शहरी</t>
+          <t>दालें</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ग्रामीण</t>
+          <t>चावल</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>यायावर / खानाबदोश</t>
+          <t>गेहूँ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>जनजातीय</t>
+          <t>जौ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता के घर किससे बनाए जाते थे ?</t>
+          <t xml:space="preserve">	सिंधु सभ्यता में वृहत् स्नानागार पाया गया है</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ईंट से</t>
+          <t>मोहनजोदड़ो में</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>बांस से</t>
+          <t>हड़प्पा में</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>पत्थर से</t>
+          <t>लोथल में</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>लकड़ी से</t>
+          <t>कालीबंगा में</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>हड़प्पावासी किस वस्तु के उत्पादन में सर्वप्रथम थे</t>
+          <t>पैमानों की खोज ने यह सिद्ध कर दिया है कि सिंधु घाटी के लोग माप और तौल से परिचित थे। यह खोज कहाँ पर हुई ?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>कपास</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>मुद्राएँ</t>
+          <t>कालीबंगन</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>कांसे के औजार</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>जौ</t>
+          <t>चहुदड़ी</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>निम्नलिखित विद्वानों में से हड़प्पा सभ्यता का सर्वप्रथम खोजकर्ता कौन था ?</t>
+          <t>हड़प्पा सभ्यता के निवासी थे</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>दयाराम सहनी</t>
+          <t>शहरी</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>सर जॉन मार्शल</t>
+          <t>ग्रामीण</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>आर० डी० बनर्जी</t>
+          <t>यायावर / खानाबदोश</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ए० कनिंघम</t>
+          <t>जनजातीय</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता का पत्तननगर (बंदरगाह) कौन-सा था ?</t>
+          <t xml:space="preserve">	सिंधु घाटी सभ्यता जानी जाती है।</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>अपने नगर नियोजन के लिए</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>रोपड़</t>
+          <t>मोहनजोदड़ो एवं हड़प्पा के लिए</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>अपने कृषि संबंधी कार्यों के लिए</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>कालीबंगन</t>
+          <t>अपने उद्योगों के लिए</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>पैमानों की खोज ने यह सिद्ध कर दिया है कि सिंधु घाटी के लोग माप और तौल से परिचित थे। यह खोज कहाँ पर हुई ?</t>
+          <t xml:space="preserve">	सिंधु घाटी की सभ्यता कहाँ तक विस्तृत थी?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>पंजाब, राजस्थान, गुजरात, उत्तर प्रदेश, हरियाणा, सिंध और बलुचिस्तान</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>कालीबंगन</t>
+          <t>जाब, राजस्थान, गुजरात, उड़ीसा और बंगाल</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>राजस्थान, बिहार, बंगाल और उड़ीसा</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>चहुदड़ी</t>
+          <t>पंजाब, दिल्ली और जम्मू-कश्मीर</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पाकालीन समाज किन वर्गों में विभक्त था ?</t>
+          <t>सिंध का नखलिस्तान / बाग' हड़प्पा सभ्यता के किस पुरास्थल को कहा गया?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>विद्वान, योद्धा, व्यापारी और श्रमिक</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>शिकारी, पुजारी, किसान और क्षत्रिय</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ब्राह्मण, क्षत्रिय, वैश्य और शूद्र</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>राजा, पुरोहित, सैनिक और शूद्र</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता का सर्वाधिक उपयुक्त नाम क्या है?</t>
+          <t>हड़प्पाकालीन लोगों ने नगरों में घरों के विन्यास के लिए कौन-सी पद्धति अपनायी - थी ?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता</t>
+          <t>ग्रीड पद्धति में</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता</t>
+          <t>त्रिभुजाकार आकृति में</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>सिंधु घाटी सभ्यता</t>
+          <t>गोलाकार आकृति में</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>कमल पुष्प की आकृति का</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>निम्न में से कौन से लक्षण सभ्यता के लोगों का सही चित्रण करता हैं 1. उनके विशाल महल और मन्दिर होते थे 2. वे देवियों और देवताओं दोनों की पूजा करते थे l 3. वे युद्ध में घोड़ों द्वारा खींचे जानेवाले रथों का प्रयोग करते थे नीचे दिए गये कूट का प्रयोग कर सही कथन को चुनिए</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
+          <t>हड़प्पा सभ्यता के सम्पूर्ण क्षेत्र का आकार किस प्रकार का था ?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>त्रिभुजाकार</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>गोलाकार</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1,2,3</t>
+          <t>आयताकार</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>वर्गाकार</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता की खोज किस वर्ष में हुई थी ?</t>
+          <t>हड़प्पा सभ्यता का सर्वाधिक मान्यता प्राप्त काल है</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1921 ई०</t>
+          <t>2500 ई०पू०-1750 ई०पू०</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1901 ई०</t>
+          <t>2800 ई०पू०-2000 ई०पू०</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1942 ई०</t>
+          <t>3500 ई०पू०-1800 ई०पू०</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1935 ई०</t>
+          <t>निश्चित नहीं हो सका है</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता के बारे में कौन-सी उक्ति सही है ?</t>
+          <t xml:space="preserve">	हड़प्पाकालीन समाज किन वर्गों में विभक्त था ?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>उन्होंने पशुपति का सम्मान करना आरंभ किया</t>
+          <t>विद्वान, योद्धा, व्यापारी और श्रमिक</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>उनकी संस्कृति सामान्यतः स्थिर नहीं थी।</t>
+          <t>शिकारी, पुजारी, किसान और क्षत्रिय</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>गाय उनके लिए पवित्र थी</t>
+          <t>ब्राह्मण, क्षत्रिय, वैश्य और शूद्र</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>उन्हें अश्वमेध का जानकारी थी</t>
+          <t>राजा, पुरोहित, सैनिक और शूद्र</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1073,1619 +1073,1617 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>जाति आधारित</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>वर्ण आधारित</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>जाति आधारित</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">	‘सिंध का नखलिस्तान / बाग' हड़प्पा सभ्यता के किस पुरास्थल को कहा गया?</t>
+          <t xml:space="preserve">	हड़प्पा एवं मोहनजोदड़ो की पुरातात्विक खुदाई के प्रभारी थे</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>सर जान मार्शल</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>कर्नल टाड</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>लाई क्लाइव</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>लाई मैकाले</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता के सम्पूर्ण क्षेत्र का आकार किस प्रकार का था ?</t>
+          <t xml:space="preserve">	हड़प्पा के काल का ताँबे का रथ किस स्थान से प्राप्त हुआ है ?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>त्रिभुजाकार</t>
+          <t>दैमावाद</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>गोलाकार</t>
+          <t>बणावली</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>आयताकार</t>
+          <t>कुणाल</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>वर्गाकार</t>
+          <t>राखीगढ़ी</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (स्थल) A. हड़प्पा B. मोहनजोदड़ो C. लोथल D. कालीबंगा सूची-II (नदी) 1. रावी 2. सिंधु 3. भोगवा 4. घग्घर</t>
+          <t>हड़प्पा सभ्यता का प्रचलित नाम है।</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 3, D → 4</t>
+          <t>मोहनजोदड़ो की सभ्यता</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A → 2, B → 1, C → 4, D → 3</t>
+          <t>सिन्धु घाटी की सभ्यता</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>A → 4, B → 3, C → 2, D → 1</t>
+          <t>लोथल सभ्यता</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 4, D → 3</t>
+          <t>सिंधु सभ्यता</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा सभ्यता के अंतर्गत हल से जोते गये खेत का साक्ष्य कहाँ से मिला है ?</t>
+          <t>हड़प्पा सभ्यता के बारे में कौन-सी उक्ति सही है ?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>उन्होंने पशुपति का सम्मान करना आरंभ किया</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>रोपड़</t>
+          <t>उनकी संस्कृति सामान्यतः स्थिर नहीं थी।</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>गाय उनके लिए पवित्र थी</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>अणावली</t>
+          <t>उन्हें अश्वमेध का जानकारी थी</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>सैंधव सभ्यता की ईटों का अलंकरण किस स्थान से मिला है?</t>
+          <t>सिंधु सभ्यता की मुद्रा में किस देवता के रामतुल्य चित्रांकन मिलता है</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>आद्य शिव</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>चन्हूदड़ो</t>
+          <t>आद्य ब्रह्मा</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>अद्य विष्णु</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>बणावली</t>
+          <t>आद्य इन्द्र</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">	मोहनजोदड़ो कहाँ स्थित है?</t>
+          <t xml:space="preserve">	निम्नलिखित में से किस हड़प्पाकालीन स्थल से युगल शवाधान का साक्ष्य मिला है</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>सिंध</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश</t>
+          <t>बणावली</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">	सिंधु सभ्यता में वृहत् स्नानागार पाया गया है</t>
+          <t xml:space="preserve">	‘सिंध का नखलिस्तान / बाग' हड़प्पा सभ्यता के किस पुरास्थल को कहा गया?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो में</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>हड़प्पा में</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>लोथल में</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>कालीबंगा में</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता की मुद्रा में किस देवता के रामतुल्य चित्रांकन मिलता है</t>
+          <t>सिंधु सभ्यता का सर्वाधिक उपयुक्त नाम क्या है?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>आद्य शिव</t>
+          <t>हड़प्पा सभ्यता</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>आद्य ब्रह्मा</t>
+          <t>सिंधु सभ्यता</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>अद्य विष्णु</t>
+          <t>सिंधु घाटी सभ्यता</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>आद्य इन्द्र</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>निम्नलिखित में से कौन-सा हड़प्पाकालीन स्थल गुजरात में था ?</t>
+          <t>हड़प्पा सभ्यता के बारे में कौन-सी उक्ति सही है ?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>उन्होंने पशुपति का सम्मान करना आरंभ किया</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>वणावली</t>
+          <t>उनकी संस्कृति सामान्यतः स्थिर नहीं थी।</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>रोपड़</t>
+          <t>गाय उनके लिए पवित्र थी</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>उन्हें अश्वमेध का जानकारी थी</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो को किस एक अन्य नाम से भी जाना जाता है ?</t>
+          <t>कपास का उत्पादन सर्वप्रथम सिन्धु क्षेत्र में हुआ, जिसे ग्रीक या यूनान के लोग किस नाम से पुकारा ?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>मृतकों का टीला (Mound of Dead)</t>
+          <t>सिन्डन (Sindon)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>दासों का टीला (Mound of Slaves)</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>कंकालों का टीला (Mound of Skeletons)</t>
+          <t>a' एवं 'b' दोनों</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>जीवितों का टीला (Mound of Living)</t>
+          <t>कॉटन (Cotton)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता का प्रचलित नाम है।</t>
+          <t>सिंधु घाटी सभ्यता के लोगों का मुख्य व्यवसाय क्या था ?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो की सभ्यता</t>
+          <t>व्यापार</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>सिन्धु घाटी की सभ्यता</t>
+          <t>पशुपालन</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>लोथल सभ्यता</t>
+          <t>शिकार</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता</t>
+          <t>कृषि</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>सैंधव स्थलों के उत्खनन से प्राप्त मुहरों पर निम्नलिखित में से किस पशु का सर्वाधिक उत्कीर्णन हुआ है ?</t>
+          <t xml:space="preserve">	हड़प्पा सभ्यता की खोज किस वर्ष में हुई थी ?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>बैल</t>
+          <t>1921 ई०</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>हाथी</t>
+          <t>1935 ई०</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>घोड़ा</t>
+          <t>1901 ई०</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>शेर</t>
+          <t>1942 ई०</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">	सिंधु घाटी सभ्यता जानी जाती है।</t>
+          <t xml:space="preserve">	हड़प्पा में एक उन्नत जल-प्रबंधन प्रणाली का पता चलता है</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>अपने नगर नियोजन के लिए</t>
+          <t>धौलावीरा में</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो एवं हड़प्पा के लिए</t>
+          <t>कालीबंगन में</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>अपने कृषि संबंधी कार्यों के लिए</t>
+          <t>आलमगीरपुर में</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>अपने उद्योगों के लिए</t>
+          <t>लोथल में</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता का कौन-सा स्थान भारत में स्थित है?</t>
+          <t>सिंधु घाटी के लोग विश्वास करते थे</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>मातृशक्ति में</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>यज्ञ प्रणाली में</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>कर्मकाण्ड में</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>आत्मा और ब्रह्म में</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>भारत में खोजा गया सबसे पहला पुराना शहर था</t>
+          <t>सिन्धु घाटी की सभ्यता के सन्दर्भ में निम्नलिखित कथनों पर विचार कीजिए - 1. यह प्रमुखत: लौकिक सभ्यता थी तथा उसमें धार्मिक तत्व, यद्यपि उपस्थित था, वर्चस्वशाली नहीं था | 2. उस काल में भारत में कपास से वस्त्र बनाये जाते थे | उपर्युक्त में से कौन-सा /कौन से कथन सही है/हैं ?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>1 और 2 दोनों</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>केवल 1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>केवल 2</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>सिंध</t>
+          <t>न तो 1 और न ही 2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>भारत में चाँदी की उपलब्धता के प्राचीनतम साक्ष्य मिलते हैं</t>
+          <t>चन्हुदड़ो के उत्खनन का निर्देशन किया था -</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>हड़प्पा संस्कृति में</t>
+          <t>जे. एच. मैके ने</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>पश्चिमी भारत की ताम्रपाषाण संस्कृति में</t>
+          <t>सर जॉन मार्शल ने</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>वैदिक संहिताओं में</t>
+          <t>आर. ई. एम. व्हीलर ने</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>चॉदी के आहत मुद्राओं में</t>
+          <t>सर ऑरेल स्टीन ने</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता के बारे में कौन-सा कथन असत्य है?</t>
+          <t>किस हड़प्पाकालीन स्थल से ‘नृत्य मुद्रा वाली स्त्री की कांस्य मूर्ति' प्राप्त हुई है?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>लोग लोहे से परिचित थे</t>
+          <t>मोहनजोदड़ो से</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>मातृदेवी की उपासना की जाती थी</t>
+          <t>कालीबंगा से</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>व्यापार और वाणिज्य उन्नत दशा में था</t>
+          <t>हड़प्पा से</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>नगरों में नालियों की सुदृढ़ व्यवस्था थी</t>
+          <t>वणावली से</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">	सूची-I को सूची-II से सुमेलित कीजिए : सूची-I A. सिंधु सभ्यता की उत्तरी सीमा B. सिंधु सभ्यता की दक्षिणी सीमा C. सिंधु सभ्यता की पूर्वी सीमा D. सिंधु सभ्यता की पश्चिमी सीमा सूची-II 1. माडा/जम्मू 2. दैमाबाद/महाराष्ट्र 3. आलमगीरपुर / उत्तर प्रदेश 4. सुत्कागेंडर/बलूचिस्तान</t>
+          <t>सिंधु सभ्यता का कौन-सा स्थान भारत में स्थित है?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 3, D → 4</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A → 2, B → 1, C → 4, D → 3</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>A → 4, B → 3, C → 2, D → 1</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 4, D → 3</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>मांडा किस नदी के किनारे स्थित था?</t>
+          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (स्थल) A. हड़प्पा B. मोहनजोदड़ो C. लोथल D. कालीबंगा सूची-II (नदी) 1. रावी 2. सिंधु 3. भोगवा 4. घग्घर</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>चेनाब</t>
+          <t>A → 1, B → 2, C → 3, D → 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>सतलज</t>
+          <t>A → 2, B → 1, C → 4, D → 3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>रावी</t>
+          <t>A → 4, B → 3, C → 2, D → 1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>सिंधु</t>
+          <t>A → 1, B → 2, C → 4, D → 3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>हड़प्पाकालीन स्थल रोपड़/ पंजाव किस नदी के किनारे स्थित था ?</t>
+          <t>सिंधु घाटी की सभ्यता निम्नलिखित में से किस सभ्यता के समकालीन नहीं थी ?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>सतलज</t>
+          <t>ग्रीक की सभ्यता</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>चेनाब</t>
+          <t>मेसोपोटामिया की सभ्यता</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>सिंधु</t>
+          <t>चीन की सभ्यता</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>रावी</t>
+          <t>मिस्र की सभ्यता</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा में एक उन्नत जल-प्रबंधन प्रणाली का पता चलता है</t>
+          <t>अफगानिस्तान स्थित सिंधु सभ्यता के स्थल हैं</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>धौलावीरा में</t>
+          <t>(a) और (b) दोनों</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>कालीबंगन में</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>आलमगीरपुर में</t>
+          <t>सुर्तागोई</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>लोथल में</t>
+          <t>मुंडीगाक</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>हड़प्पा के मिट्टी के बर्तनों पर सामान्यतः किस रंग का उपयोग हुआ था?</t>
+          <t>निम्नलिखित में कौन-सा सिंधु स्थल समुद्र तट पर स्थित नहीं था ?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>लाल</t>
+          <t>कोटदीजी</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>नीला-हरा</t>
+          <t>बालाकोट</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>पांडु</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>नीला</t>
+          <t>सुरकोटदा</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>सिन्धु सभ्यता निम्नलिखित में से किस युग में पड़ता है?</t>
+          <t>कथन (A) ; हड़प्पा तथा मोहनजोदड़ों अय विलुप्त हो गए हैं। कारण (R) : वे उत्खनन के दौरान प्रकट हुए थे।</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>आद्य ऐतिहासिक काल (Proto-Historical Period)</t>
+          <t>A और R दोनों सही हैं तथा R, A का सही स्पष्टीकरण है</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>उत्तर-प्रागैतिहासिक काल (Post-Historical Period)</t>
+          <t>A और R दोनों सही हैं किन्तु R, A का सही स्पष्टीकरण नहीं है</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>प्रागतिहासिक काल (Pre-Historical Period)</t>
+          <t>A सही है किन्तु R गलत है</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ऐतिहासिक काल (Historical Period)</t>
+          <t>A गलत है किन्तु R सही है</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>सिंधु घाटी सभ्यता की विकसित अवस्था में निम्नलिखित में से किस स्थल में घरों में कुँओं के अवशेष मिले हैं?</t>
+          <t>सिंधु सभ्यता के बारे में कौन-सा कथन असत्य है?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>लोग लोहे से परिचित थे</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>मातृदेवी की उपासना की जाती थी</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>व्यापार और वाणिज्य उन्नत दशा में था</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>हडपा</t>
+          <t>नगरों में नालियों की सुदृढ़ व्यवस्था थी</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>सिंधु घाटी सभ्यता को खोज निकालने में जिन दो भारतीय का नाम जुड़ा है</t>
+          <t>सिंधु सभ्यता के घर किससे बनाए जाते थे ?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>दयाराम साहनी एवं राखालदास बनर्जी</t>
+          <t>ईंट से</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>जान मार्शल एवं ईश्वरी प्रसाद</t>
+          <t>बांस से</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>आशीर्वादीलाल श्रीवास्तव एवं रंगनाथ राव</t>
+          <t>पत्थर से</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>माधोस्वरूप वत्स एवं वी० बी० राव</t>
+          <t>लकड़ी से</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">	रंगपुर जहाँ हड़प्पा की समकालीन सभ्यता थी, है -</t>
+          <t>हड़प्पाकालीन स्थलों में अभी तक किस धातु की प्राप्ति नहीं हुई है ?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>सौराष्ट्र में</t>
+          <t>लोहा</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>राजस्थान में</t>
+          <t>चांदी</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश में</t>
+          <t>स्वर्ण</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>पंजाब में</t>
+          <t>तांबा</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा एवं मोहनजोदड़ो की पुरातात्विक खुदाई के प्रभारी थे</t>
+          <t>भारत में खोजा गया सबसे पहला पुराना शहर था</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>सर जान मार्शल</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>कर्नल टाड</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>लाई क्लाइव</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>लाई मैकाले</t>
+          <t>सिंध</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>निम्न में से किस पशु की आकृति जो मुहर पर मिली है, जिससे ज्ञात होता है, कि सिंधु घाटी एवं मेसोपोटामिया की सभ्यताओं के मध्य व्यापारिक संबंध थे</t>
+          <t>हड़प्पा के मिट्टी के बर्तनों पर सामान्यतः किस रंग का उपयोग हुआ था?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>बैल</t>
+          <t>लाल</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>गधा</t>
+          <t>नीला-हरा</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>हाथी</t>
+          <t>पांडु</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>घोड़ा</t>
+          <t>नीला</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>सिंधु घाटी के लोग विश्वास करते थे</t>
+          <t>हड़प्पावासी लाजवर्द-Lapislazuli- (भवन निर्माण की सामग्री) का आयात कहाँ से करते थे ?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>मातृशक्ति में</t>
+          <t>हिन्दूकुश क्षेत्र के बदख्शा से</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>यज्ञ प्रणाली में</t>
+          <t>ईरान से</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>कर्मकाण्ड में</t>
+          <t>दक्षिण भारत से</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>आत्मा और ब्रह्म में</t>
+          <t>बलूचिस्तान से</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>निम्नलिखित में कौन-सा सिंधु स्थल समुद्र तट पर स्थित नहीं था ?</t>
+          <t>निम्नलिखित में से कौन-सा हड़प्पाकालीन स्थल गुजरात में था ?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>कोटदीजी</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>बालाकोट</t>
+          <t>वणावली</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>रोपड़</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>सुरकोटदा</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>निम्नलिखित में से कौन मोहनजोदड़ो की सबसे बड़ी इमारत मानी जाती है?</t>
+          <t>हड़प्पावासी किस वस्तु के उत्पादन में सर्वप्रथम थे</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>विशाल अन्नागार / धान्यकोठार</t>
+          <t>कपास</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>विशाल स्नानागार</t>
+          <t>मुद्राएँ</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>कांसे के औजार</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>सभा भवन</t>
+          <t>जौ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>हड़प्पाकालीन लोगों ने नगरों में घरों के विन्यास के लिए कौन-सी पद्धति अपनायी - थी ?</t>
+          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (हडप्पीय स्थल) A. मांडा B. दायमाबाद C. कालीबंगा D. राखीगढ़ी सूची-II (स्थिति) 1. राजस्थान 2. हरियाणा 3. जम्मू-कश्मीर 4. महाराष्ट्र</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ग्रीड पद्धति में</t>
+          <t>A → 3, B → 4, C → 1, D → 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>त्रिभुजाकार आकृति में</t>
+          <t>A → 4, B → 1, C → 2, D → 3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>गोलाकार आकृति में</t>
+          <t>A → 2, B → 3, C → 4, D → 1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>कमल पुष्प की आकृति का</t>
+          <t>A → 1, B → 2, C → 3, D → 4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (प्राचीन स्थल) A. लोथल B. कालीबंगन C. धौलावीर D. बनवाली सूची-II (पुरातत्वीय अवशेष) 1. जूता हुआ खेत 2. गोदीबाड़ा (Dockyaard) 3. पकी मिट्टी की बनी हुई हल की प्रतिकृति 4. हड़प्पाई लिपि के बड़े आकार के दस चिन्हों वाला एक शिलालेख</t>
+          <t>किस हड़प्पाकालीन स्थल से प्राप्त जार पर चोंच में मछली दबाए चिड़िया एवं पेड़ के नीचे खड़ी लोमड़ी का चित्रांकन मिलता है, जो 'पंचतंत्र ' के लोमड़ी की कहानी सदृश्य है ?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>A → 2, B → 1, C → 4, D → 3</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>A → 3, B → 1, C → 4, D → 2</t>
+          <t>रंगपुर</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 4, D → 3</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 3, D → 4</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>निम्नलिखित पशुओं में से किस एक का हड़प्पा सभ्यता में पाई मुहरों और टेराकोटा कलाकृतियों में निरूपण / अंकन नहीं हुआ था ?</t>
+          <t>किस हड़प्पाकालीन स्थल से ‘पुजारी की प्रस्तर मूर्ति प्राप्त हुई है?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>शेर</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>हाथी</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>गैंडा</t>
+          <t>रंगपुर</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>बाघ</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पावासी किस धातु से परिचित नहीं थे ?</t>
+          <t>निम्नलिखित में से किस पदार्थ का उपयोग हड़प्पा काल की मुद्राओं के निर्माण में मुख्य रूप से किया गया था ?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>सेलखड़ी (steatite)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>कांसा</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ताँवा</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>लोहा</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>टीन एवं सीसा</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>तांबा एवं कांसा</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>सोना एवं चांदी</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">	निम्नलिखित में से किस हड़प्पाकालीन स्थल से युगल शवाधान का साक्ष्य मिला है</t>
+          <t xml:space="preserve">	सूची-I को सूची-II से सुमेलित कीजिए : सूची-I A. सिंधु सभ्यता की उत्तरी सीमा B. सिंधु सभ्यता की दक्षिणी सीमा C. सिंधु सभ्यता की पूर्वी सीमा D. सिंधु सभ्यता की पश्चिमी सीमा सूची-II 1. माडा/जम्मू 2. दैमाबाद/महाराष्ट्र 3. आलमगीरपुर / उत्तर प्रदेश 4. सुत्कागेंडर/बलूचिस्तान</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>A → 1, B → 2, C → 3, D → 4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>A → 2, B → 1, C → 4, D → 3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>बणावली</t>
+          <t>A → 4, B → 3, C → 2, D → 1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>A → 1, B → 2, C → 4, D → 3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>कपास का उत्पादन सर्वप्रथम सिन्धु क्षेत्र में हुआ, जिसे ग्रीक या यूनान के लोग किस नाम से पुकारा ?</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>सिन्डन (Sindon)</t>
-        </is>
+          <t>निम्न में से कौन से लक्षण सभ्यता के लोगों का सही चित्रण करता हैं 1. उनके विशाल महल और मन्दिर होते थे 2. वे देवियों और देवताओं दोनों की पूजा करते थे l 3. वे युद्ध में घोड़ों द्वारा खींचे जानेवाले रथों का प्रयोग करते थे नीचे दिए गये कूट का प्रयोग कर सही कथन को चुनिए</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>a' एवं 'b' दोनों</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>कॉटन (Cotton)</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा के काल का ताँबे का रथ किस स्थान से प्राप्त हुआ है ?</t>
+          <t>हड़प्पा के लोगों की सामाजिक पद्धति...... थी</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>दैमावाद</t>
+          <t>उचित समतावादी</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>बणावली</t>
+          <t>दास-श्रमिक आधारित</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>कुणाल</t>
+          <t>वर्ण आधारित</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>राखीगढ़ी</t>
+          <t>जाति आधारित</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>हड़प्पावासी किन-किन धातुओं का आयात करते थे ? उत्तर कूट में दें - कूट : 1. चाँदी 2. टिन 3. सोना</t>
+          <t>कौन-कौन से नगर सिंधु सभ्यता के बंदरगाह नगर थे ?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1, 2 एवं 3</t>
+          <t>इनमें से सभी</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1 एवं 2</t>
+          <t>कुनतासी</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1 एवं 3</t>
+          <t>अल्लाहदिनो एवं बालाकोट</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2 एवं 3</t>
+          <t>लोथल एवं सुत्कागेंडर</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>हड़प्पावासी लाजवर्द-Lapislazuli- (भवन निर्माण की सामग्री) का आयात कहाँ से करते थे ?</t>
+          <t>निम्नलिखित विद्वानों में से हड़प्पा सभ्यता का सर्वप्रथम खोजकर्ता कौन था ?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>हिन्दूकुश क्षेत्र के बदख्शा से</t>
+          <t>दयाराम सहनी</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ईरान से</t>
+          <t>सर जॉन मार्शल</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>दक्षिण भारत से</t>
+          <t>आर० डी० बनर्जी</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>बलूचिस्तान से</t>
+          <t>ए० कनिंघम</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>अफगानिस्तान स्थित सिंधु सभ्यता के स्थल हैं</t>
+          <t>निम्न में से किस पशु की आकृति जो मुहर पर मिली है, जिससे ज्ञात होता है, कि सिंधु घाटी एवं मेसोपोटामिया की सभ्यताओं के मध्य व्यापारिक संबंध थे</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>(a) और (b) दोनों</t>
+          <t>बैल</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>गधा</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>सुर्तागोई</t>
+          <t>हाथी</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>मुंडीगाक</t>
+          <t>घोड़ा</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>कौन-कौन से नगर सिंधु सभ्यता के बंदरगाह नगर थे ?</t>
+          <t xml:space="preserve">	हड़प्पा सभ्यता के अंतर्गत हल से जोते गये खेत का साक्ष्य कहाँ से मिला है ?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>इनमें से सभी</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>कुनतासी</t>
+          <t>रोपड़</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>अल्लाहदिनो एवं बालाकोट</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>लोथल एवं सुत्कागेंडर</t>
+          <t>अणावली</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो से प्राप्त पशुपति शिव/ आद्य शिव मुहर में किन किन जानवरों का अंकन हुआ है ?</t>
+          <t xml:space="preserve">	हड़प्पा सभ्यता किस युग की थी ?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>इनमें से सभी</t>
+          <t>कांस्य युग</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>हिरण</t>
+          <t>नवपाषाण युग</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>गैंडा एवं भैंसा</t>
+          <t>पुरापाषाण युग</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>व्याघ्र एवं हाथी</t>
+          <t>लौह युग</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>किस हड़प्पाकालीन स्थल से ‘नृत्य मुद्रा वाली स्त्री की कांस्य मूर्ति' प्राप्त हुई है?</t>
+          <t>सिंधु घाटी सभ्यता की विकसित अवस्था में निम्नलिखित में से किस स्थल में घरों में कुँओं के अवशेष मिले हैं?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो से</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>कालीबंगा से</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>हड़प्पा से</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>वणावली से</t>
+          <t>हडपा</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>किस हड़प्पाकालीन स्थल से ‘पुजारी की प्रस्तर मूर्ति प्राप्त हुई है?</t>
+          <t>मोहनजोदड़ो को किस एक अन्य नाम से भी जाना जाता है ?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>मृतकों का टीला (Mound of Dead)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>दासों का टीला (Mound of Slaves)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>रंगपुर</t>
+          <t>कंकालों का टीला (Mound of Skeletons)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>जीवितों का टीला (Mound of Living)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>किस सिंधुकालीन स्थल से एक ईट पर बिल्ली का पीछा करते हुए कुत्ते के पंजों के निशान मिले हैं ?</t>
+          <t>सिंधु घाटी की सभ्यता में घोड़े के अवशेष कहाँ मिले हैं ?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>चन्हुदड़ो</t>
+          <t>सुरकोटदा</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>वणावली</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>लोथल</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>मोहनजोदड़ो</t>
-        </is>
-      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>किस हड़प्पाकालीन स्थल से प्राप्त जार पर चोंच में मछली दबाए चिड़िया एवं पेड़ के नीचे खड़ी लोमड़ी का चित्रांकन मिलता है, जो 'पंचतंत्र ' के लोमड़ी की कहानी सदृश्य है ?</t>
+          <t>सिंधु घाटी स्थल कालीबंगन किस प्रदेश में है ?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>राजस्थान में</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>रंगपुर</t>
+          <t>गुजरात में</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>मध्य प्रदेश में</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>उत्तर प्रदेश में</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>स्वातंत्र्योत्तर भारत में सबसे अधिक संख्या में हड़पायुगीन स्थलों की खोज किस प्रांत में हुई है?</t>
+          <t>हड़प्पावासी किन-किन धातुओं का आयात करते थे ? उत्तर कूट में दें - कूट : 1. चाँदी 2. टिन 3. सोना</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>1, 2 एवं 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>राजस्थान</t>
+          <t>1 एवं 2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>पंजाब और हरियाणा</t>
+          <t>1 एवं 3</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>उत्तर-पश्चिमी उत्तर प्रदेश</t>
+          <t>2 एवं 3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">	निम्नलिखित में से कौन-सी फसल हड़प्पाकालीन लोगों द्वारा उत्पादित नहीं की जाती थी?</t>
+          <t>हड़प्पाकालीन स्थल रोपड़/ पंजाव किस नदी के किनारे स्थित था ?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>दालें</t>
+          <t>सतलज</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>चावल</t>
+          <t>चेनाब</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>गेहूँ</t>
+          <t>सिंधु</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>जौ</t>
+          <t>रावी</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>कथन (A) ; हड़प्पा तथा मोहनजोदड़ों अय विलुप्त हो गए हैं। कारण (R) : वे उत्खनन के दौरान प्रकट हुए थे।</t>
+          <t>किस पशु के अवशेष सिंधु घाटी सभ्यता में प्राप्त नहीं हुए हैं</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>A और R दोनों सही हैं तथा R, A का सही स्पष्टीकरण है</t>
+          <t>शेर</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>A और R दोनों सही हैं किन्तु R, A का सही स्पष्टीकरण नहीं है</t>
+          <t>घोड़ा</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>A सही है किन्तु R गलत है</t>
+          <t>गाय</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>A गलत है किन्तु R सही है</t>
+          <t>हाथी</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>सिन्धु घाटी की सभ्यता के सन्दर्भ में निम्नलिखित कथनों पर विचार कीजिए - 1. यह प्रमुखत: लौकिक सभ्यता थी तथा उसमें धार्मिक तत्व, यद्यपि उपस्थित था, वर्चस्वशाली नहीं था | 2. उस काल में भारत में कपास से वस्त्र बनाये जाते थे | उपर्युक्त में से कौन-सा /कौन से कथन सही है/हैं ?</t>
+          <t>सिंधु घाटी सभ्यता को खोज निकालने में जिन दो भारतीय का नाम जुड़ा है</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1 और 2 दोनों</t>
+          <t>दयाराम साहनी एवं राखालदास बनर्जी</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>केवल 1</t>
+          <t>जान मार्शल एवं ईश्वरी प्रसाद</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>केवल 2</t>
+          <t>आशीर्वादीलाल श्रीवास्तव एवं रंगनाथ राव</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>न तो 1 और न ही 2</t>
+          <t>माधोस्वरूप वत्स एवं वी० बी० राव</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (हडप्पीय स्थल) A. मांडा B. दायमाबाद C. कालीबंगा D. राखीगढ़ी सूची-II (स्थिति) 1. राजस्थान 2. हरियाणा 3. जम्मू-कश्मीर 4. महाराष्ट्र</t>
+          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (प्राचीन स्थल) A. लोथल B. कालीबंगन C. धौलावीर D. बनवाली सूची-II (पुरातत्वीय अवशेष) 1. जूता हुआ खेत 2. गोदीबाड़ा (Dockyaard) 3. पकी मिट्टी की बनी हुई हल की प्रतिकृति 4. हड़प्पाई लिपि के बड़े आकार के दस चिन्हों वाला एक शिलालेख</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>A → 3, B → 4, C → 1, D → 2</t>
+          <t>A → 2, B → 1, C → 4, D → 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>A → 4, B → 1, C → 2, D → 3</t>
+          <t>A → 3, B → 1, C → 4, D → 2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>A → 2, B → 3, C → 4, D → 1</t>
+          <t>A → 1, B → 2, C → 4, D → 3</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2697,246 +2695,248 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>हड़प्पाकालीन स्थलों में अभी तक किस धातु की प्राप्ति नहीं हुई है ?</t>
+          <t>सैंधव स्थलों के उत्खनन से प्राप्त मुहरों पर निम्नलिखित में से किस पशु का सर्वाधिक उत्कीर्णन हुआ है ?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>लोहा</t>
+          <t>बैल</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>चांदी</t>
+          <t>हाथी</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>स्वर्ण</t>
+          <t>घोड़ा</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>तांबा</t>
+          <t>शेर</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>किस पशु के अवशेष सिंधु घाटी सभ्यता में प्राप्त नहीं हुए हैं</t>
+          <t>मोहनजोदड़ो से प्राप्त पशुपति शिव/ आद्य शिव मुहर में किन किन जानवरों का अंकन हुआ है ?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>शेर</t>
+          <t>इनमें से सभी</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>घोड़ा</t>
+          <t>हिरण</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>गाय</t>
+          <t>गैंडा एवं भैंसा</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>हाथी</t>
+          <t>व्याघ्र एवं हाथी</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>चन्हुदड़ो के उत्खनन का निर्देशन किया था -</t>
+          <t>सैंधव सभ्यता की ईटों का अलंकरण किस स्थान से मिला है?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>जे. एच. मैके ने</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>सर जॉन मार्शल ने</t>
+          <t>चन्हूदड़ो</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>आर. ई. एम. व्हीलर ने</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>सर ऑरेल स्टीन ने</t>
+          <t>बणावली</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>निम्न में से कौन से लक्षण सभ्यता के लोगों का सही चित्रण करता हैं 1. उनके विशाल महल और मन्दिर होते थे 2. वे देवियों और देवताओं दोनों की पूजा करते थे l 3. वे युद्ध में घोड़ों द्वारा खींचे जानेवाले रथों का प्रयोग करते थे नीचे दिए गये कूट का प्रयोग कर सही कथन को चुनिए</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>2</v>
+          <t xml:space="preserve">	मोहनजोदड़ो कहाँ स्थित है?</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>सिंध</t>
+        </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1,2,3</t>
+          <t>उत्तर प्रदेश</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा सभ्यता की खोज किस वर्ष में हुई थी ?</t>
+          <t>मांडा किस नदी के किनारे स्थित था?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1921 ई०</t>
+          <t>चेनाब</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1935 ई०</t>
+          <t>सतलज</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1901 ई०</t>
+          <t>रावी</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1942 ई०</t>
+          <t>सिंधु</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता के बारे में कौन-सी उक्ति सही है ?</t>
+          <t>स्वातंत्र्योत्तर भारत में सबसे अधिक संख्या में हड़पायुगीन स्थलों की खोज किस प्रांत में हुई है?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>उन्होंने पशुपति का सम्मान करना आरंभ किया</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>उनकी संस्कृति सामान्यतः स्थिर नहीं थी।</t>
+          <t>राजस्थान</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>गाय उनके लिए पवित्र थी</t>
+          <t>पंजाब और हरियाणा</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>उन्हें अश्वमेध का जानकारी थी</t>
+          <t>उत्तर-पश्चिमी उत्तर प्रदेश</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>हड़प्पा के लोगों की सामाजिक पद्धति...... थी</t>
+          <t xml:space="preserve">	हड़प्पावासी किस धातु से परिचित नहीं थे ?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>उचित समतावादी</t>
+          <t>लोहा</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>दास-श्रमिक आधारित</t>
+          <t>टीन एवं सीसा</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>जाति आधारित</t>
+          <t>तांबा एवं कांसा</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>वर्ण आधारित</t>
+          <t>सोना एवं चांदी</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>सिंध का नखलिस्तान / बाग' हड़प्पा सभ्यता के किस पुरास्थल को कहा गया?</t>
+          <t>सिन्धु सभ्यता निम्नलिखित में से किस युग में पड़ता है?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>आद्य ऐतिहासिक काल (Proto-Historical Period)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>उत्तर-प्रागैतिहासिक काल (Post-Historical Period)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>प्रागतिहासिक काल (Pre-Historical Period)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>ऐतिहासिक काल (Historical Period)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>

--- a/Data/indus.xlsx
+++ b/Data/indus.xlsx
@@ -467,799 +467,797 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता का पत्तननगर (बंदरगाह) कौन-सा था ?</t>
+          <t>निम्नलिखित में कौन-सा सिंधु स्थल समुद्र तट पर स्थित नहीं था ?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>कोटदीजी</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>बालाकोट</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>लोथल</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>रोपड़</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>मोहनजोदड़ो</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>कालीबंगन</t>
+          <t>सुरकोटदा</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>निम्नलिखित पशुओं में से किस एक का हड़प्पा सभ्यता में पाई मुहरों और टेराकोटा कलाकृतियों में निरूपण / अंकन नहीं हुआ था ?</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>शेर</t>
-        </is>
+          <t>निम्न में से कौन से लक्षण सभ्यता के लोगों का सही चित्रण करता हैं 1. उनके विशाल महल और मन्दिर होते थे 2. वे देवियों और देवताओं दोनों की पूजा करते थे l 3. वे युद्ध में घोड़ों द्वारा खींचे जानेवाले रथों का प्रयोग करते थे नीचे दिए गये कूट का प्रयोग कर सही कथन को चुनिए</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>हाथी</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>गैंडा</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>बाघ</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>किस सिंधुकालीन स्थल से एक ईट पर बिल्ली का पीछा करते हुए कुत्ते के पंजों के निशान मिले हैं ?</t>
+          <t>किस हड़प्पाकालीन स्थल से ‘पुजारी की प्रस्तर मूर्ति प्राप्त हुई है?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>चन्हुदड़ो</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>मोहनजोदड़ो</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>रंगपुर</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>लोथल</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>मोहनजोदड़ो</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>निम्नलिखित में से कौन मोहनजोदड़ो की सबसे बड़ी इमारत मानी जाती है?</t>
+          <t>भारत में चाँदी की उपलब्धता के प्राचीनतम साक्ष्य मिलते हैं</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>विशाल अन्नागार / धान्यकोठार</t>
+          <t>हड़प्पा संस्कृति में</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>विशाल स्नानागार</t>
+          <t>पश्चिमी भारत की ताम्रपाषाण संस्कृति में</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>वैदिक संहिताओं में</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>सभा भवन</t>
+          <t>चॉदी के आहत मुद्राओं में</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता की खोज किस वर्ष में हुई थी ?</t>
+          <t>सिन्धु घाटी की सभ्यता के सन्दर्भ में निम्नलिखित कथनों पर विचार कीजिए - 1. यह प्रमुखत: लौकिक सभ्यता थी तथा उसमें धार्मिक तत्व, यद्यपि उपस्थित था, वर्चस्वशाली नहीं था | 2. उस काल में भारत में कपास से वस्त्र बनाये जाते थे | उपर्युक्त में से कौन-सा /कौन से कथन सही है/हैं ?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1921 ई०</t>
+          <t>1 और 2 दोनों</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1901 ई०</t>
+          <t>केवल 1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1942 ई०</t>
+          <t>केवल 2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1935 ई०</t>
+          <t>न तो 1 और न ही 2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">	रंगपुर जहाँ हड़प्पा की समकालीन सभ्यता थी, है -</t>
+          <t>सिंध का नखलिस्तान / बाग' हड़प्पा सभ्यता के किस पुरास्थल को कहा गया?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>सौराष्ट्र में</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>राजस्थान में</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश में</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>पंजाब में</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>भारत में चाँदी की उपलब्धता के प्राचीनतम साक्ष्य मिलते हैं</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>हड़प्पा संस्कृति में</t>
-        </is>
+          <t>निम्न में से कौन से लक्षण सभ्यता के लोगों का सही चित्रण करता हैं 1. उनके विशाल महल और मन्दिर होते थे 2. वे देवियों और देवताओं दोनों की पूजा करते थे l 3. वे युद्ध में घोड़ों द्वारा खींचे जानेवाले रथों का प्रयोग करते थे नीचे दिए गये कूट का प्रयोग कर सही कथन को चुनिए</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>पश्चिमी भारत की ताम्रपाषाण संस्कृति में</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>वैदिक संहिताओं में</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>चॉदी के आहत मुद्राओं में</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>निम्न में से कौन से लक्षण सभ्यता के लोगों का सही चित्रण करता हैं 1. उनके विशाल महल और मन्दिर होते थे 2. वे देवियों और देवताओं दोनों की पूजा करते थे l 3. वे युद्ध में घोड़ों द्वारा खींचे जानेवाले रथों का प्रयोग करते थे नीचे दिए गये कूट का प्रयोग कर सही कथन को चुनिए</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
+          <t>पैमानों की खोज ने यह सिद्ध कर दिया है कि सिंधु घाटी के लोग माप और तौल से परिचित थे। यह खोज कहाँ पर हुई ?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>लोथल</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>कालीबंगन</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1,2,3</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>चहुदड़ी</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">	निम्नलिखित में से कौन-सी फसल हड़प्पाकालीन लोगों द्वारा उत्पादित नहीं की जाती थी?</t>
+          <t xml:space="preserve">	मोहनजोदड़ो कहाँ स्थित है?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>दालें</t>
+          <t>सिंध</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>चावल</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>गेहूँ</t>
+          <t>उत्तर प्रदेश</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>जौ</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">	सिंधु सभ्यता में वृहत् स्नानागार पाया गया है</t>
+          <t xml:space="preserve">	हड़प्पा सभ्यता की खोज किस वर्ष में हुई थी ?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो में</t>
+          <t>1921 ई०</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>हड़प्पा में</t>
+          <t>1935 ई०</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>लोथल में</t>
+          <t>1901 ई०</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>कालीबंगा में</t>
+          <t>1942 ई०</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>पैमानों की खोज ने यह सिद्ध कर दिया है कि सिंधु घाटी के लोग माप और तौल से परिचित थे। यह खोज कहाँ पर हुई ?</t>
+          <t xml:space="preserve">	हड़प्पा में एक उन्नत जल-प्रबंधन प्रणाली का पता चलता है</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>धौलावीरा में</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>कालीबंगन</t>
+          <t>कालीबंगन में</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>आलमगीरपुर में</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>चहुदड़ी</t>
+          <t>लोथल में</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता के निवासी थे</t>
+          <t xml:space="preserve">	हड़प्पा के काल का ताँबे का रथ किस स्थान से प्राप्त हुआ है ?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>शहरी</t>
+          <t>दैमावाद</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ग्रामीण</t>
+          <t>बणावली</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>यायावर / खानाबदोश</t>
+          <t>कुणाल</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>जनजातीय</t>
+          <t>राखीगढ़ी</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">	सिंधु घाटी सभ्यता जानी जाती है।</t>
+          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (स्थल) A. हड़प्पा B. मोहनजोदड़ो C. लोथल D. कालीबंगा सूची-II (नदी) 1. रावी 2. सिंधु 3. भोगवा 4. घग्घर</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>अपने नगर नियोजन के लिए</t>
+          <t>A → 1, B → 2, C → 3, D → 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो एवं हड़प्पा के लिए</t>
+          <t>A → 2, B → 1, C → 4, D → 3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>अपने कृषि संबंधी कार्यों के लिए</t>
+          <t>A → 4, B → 3, C → 2, D → 1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>अपने उद्योगों के लिए</t>
+          <t>A → 1, B → 2, C → 4, D → 3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">	सिंधु घाटी की सभ्यता कहाँ तक विस्तृत थी?</t>
+          <t>हड़प्पावासी किन-किन धातुओं का आयात करते थे ? उत्तर कूट में दें - कूट : 1. चाँदी 2. टिन 3. सोना</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>पंजाब, राजस्थान, गुजरात, उत्तर प्रदेश, हरियाणा, सिंध और बलुचिस्तान</t>
+          <t>1, 2 एवं 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>जाब, राजस्थान, गुजरात, उड़ीसा और बंगाल</t>
+          <t>1 एवं 2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>राजस्थान, बिहार, बंगाल और उड़ीसा</t>
+          <t>1 एवं 3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>पंजाब, दिल्ली और जम्मू-कश्मीर</t>
+          <t>2 एवं 3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>सिंध का नखलिस्तान / बाग' हड़प्पा सभ्यता के किस पुरास्थल को कहा गया?</t>
+          <t>किस हड़प्पाकालीन स्थल से ‘नृत्य मुद्रा वाली स्त्री की कांस्य मूर्ति' प्राप्त हुई है?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>मोहनजोदड़ो से</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>कालीबंगा से</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>हड़प्पा से</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>वणावली से</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>हड़प्पाकालीन लोगों ने नगरों में घरों के विन्यास के लिए कौन-सी पद्धति अपनायी - थी ?</t>
+          <t xml:space="preserve">	सिंधु सभ्यता में वृहत् स्नानागार पाया गया है</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ग्रीड पद्धति में</t>
+          <t>मोहनजोदड़ो में</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>त्रिभुजाकार आकृति में</t>
+          <t>हड़प्पा में</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>गोलाकार आकृति में</t>
+          <t>लोथल में</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>कमल पुष्प की आकृति का</t>
+          <t>कालीबंगा में</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता के सम्पूर्ण क्षेत्र का आकार किस प्रकार का था ?</t>
+          <t>निम्न में से किस पशु की आकृति जो मुहर पर मिली है, जिससे ज्ञात होता है, कि सिंधु घाटी एवं मेसोपोटामिया की सभ्यताओं के मध्य व्यापारिक संबंध थे</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>त्रिभुजाकार</t>
+          <t>बैल</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>गोलाकार</t>
+          <t>गधा</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>आयताकार</t>
+          <t>हाथी</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>वर्गाकार</t>
+          <t>घोड़ा</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता का सर्वाधिक मान्यता प्राप्त काल है</t>
+          <t>हड़प्पाकालीन लोगों ने नगरों में घरों के विन्यास के लिए कौन-सी पद्धति अपनायी - थी ?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2500 ई०पू०-1750 ई०पू०</t>
+          <t>ग्रीड पद्धति में</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2800 ई०पू०-2000 ई०पू०</t>
+          <t>त्रिभुजाकार आकृति में</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3500 ई०पू०-1800 ई०पू०</t>
+          <t>गोलाकार आकृति में</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>निश्चित नहीं हो सका है</t>
+          <t>कमल पुष्प की आकृति का</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पाकालीन समाज किन वर्गों में विभक्त था ?</t>
+          <t>निम्नलिखित पशुओं में से किस एक का हड़प्पा सभ्यता में पाई मुहरों और टेराकोटा कलाकृतियों में निरूपण / अंकन नहीं हुआ था ?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>विद्वान, योद्धा, व्यापारी और श्रमिक</t>
+          <t>शेर</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>शिकारी, पुजारी, किसान और क्षत्रिय</t>
+          <t>हाथी</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ब्राह्मण, क्षत्रिय, वैश्य और शूद्र</t>
+          <t>गैंडा</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>राजा, पुरोहित, सैनिक और शूद्र</t>
+          <t>बाघ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>हड़प्पा के लोगों की सामाजिक पद्धति...... थी</t>
+          <t xml:space="preserve">	सिंधु घाटी की सभ्यता कहाँ तक विस्तृत थी?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>उचित समतावादी</t>
+          <t>पंजाब, राजस्थान, गुजरात, उत्तर प्रदेश, हरियाणा, सिंध और बलुचिस्तान</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>दास-श्रमिक आधारित</t>
+          <t>जाब, राजस्थान, गुजरात, उड़ीसा और बंगाल</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>जाति आधारित</t>
+          <t>राजस्थान, बिहार, बंगाल और उड़ीसा</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>वर्ण आधारित</t>
+          <t>पंजाब, दिल्ली और जम्मू-कश्मीर</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा एवं मोहनजोदड़ो की पुरातात्विक खुदाई के प्रभारी थे</t>
+          <t>हड़प्पावासी लाजवर्द-Lapislazuli- (भवन निर्माण की सामग्री) का आयात कहाँ से करते थे ?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>सर जान मार्शल</t>
+          <t>हिन्दूकुश क्षेत्र के बदख्शा से</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>कर्नल टाड</t>
+          <t>ईरान से</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>लाई क्लाइव</t>
+          <t>दक्षिण भारत से</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>लाई मैकाले</t>
+          <t>बलूचिस्तान से</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा के काल का ताँबे का रथ किस स्थान से प्राप्त हुआ है ?</t>
+          <t>हड़प्पा सभ्यता के बारे में कौन-सी उक्ति सही है ?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>दैमावाद</t>
+          <t>उन्होंने पशुपति का सम्मान करना आरंभ किया</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>बणावली</t>
+          <t>उनकी संस्कृति सामान्यतः स्थिर नहीं थी।</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>कुणाल</t>
+          <t>गाय उनके लिए पवित्र थी</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>राखीगढ़ी</t>
+          <t>उन्हें अश्वमेध का जानकारी थी</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता का प्रचलित नाम है।</t>
+          <t>निम्नलिखित में से कौन मोहनजोदड़ो की सबसे बड़ी इमारत मानी जाती है?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो की सभ्यता</t>
+          <t>विशाल अन्नागार / धान्यकोठार</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>सिन्धु घाटी की सभ्यता</t>
+          <t>विशाल स्नानागार</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>लोथल सभ्यता</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता</t>
+          <t>सभा भवन</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता के बारे में कौन-सी उक्ति सही है ?</t>
+          <t>हड़प्पावासी किस वस्तु के उत्पादन में सर्वप्रथम थे</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>उन्होंने पशुपति का सम्मान करना आरंभ किया</t>
+          <t>कपास</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>उनकी संस्कृति सामान्यतः स्थिर नहीं थी।</t>
+          <t>मुद्राएँ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>गाय उनके लिए पवित्र थी</t>
+          <t>कांसे के औजार</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>उन्हें अश्वमेध का जानकारी थी</t>
+          <t>जौ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता की मुद्रा में किस देवता के रामतुल्य चित्रांकन मिलता है</t>
+          <t>निम्नलिखित में से किस पदार्थ का उपयोग हड़प्पा काल की मुद्राओं के निर्माण में मुख्य रूप से किया गया था ?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>आद्य शिव</t>
+          <t>सेलखड़ी (steatite)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>आद्य ब्रह्मा</t>
+          <t>कांसा</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>अद्य विष्णु</t>
+          <t>ताँवा</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>आद्य इन्द्र</t>
+          <t>लोहा</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">	निम्नलिखित में से किस हड़प्पाकालीन स्थल से युगल शवाधान का साक्ष्य मिला है</t>
+          <t xml:space="preserve">	‘सिंध का नखलिस्तान / बाग' हड़प्पा सभ्यता के किस पुरास्थल को कहा गया?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>मोहनजोदड़ो</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>लोथल</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>कालीबंगा</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>बणावली</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1271,1621 +1269,1623 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">	‘सिंध का नखलिस्तान / बाग' हड़प्पा सभ्यता के किस पुरास्थल को कहा गया?</t>
+          <t>हड़प्पा के लोगों की सामाजिक पद्धति...... थी</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>उचित समतावादी</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>दास-श्रमिक आधारित</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>जाति आधारित</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>वर्ण आधारित</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता का सर्वाधिक उपयुक्त नाम क्या है?</t>
+          <t>हड़प्पा सभ्यता के बारे में कौन-सी उक्ति सही है ?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता</t>
+          <t>उन्होंने पशुपति का सम्मान करना आरंभ किया</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता</t>
+          <t>उनकी संस्कृति सामान्यतः स्थिर नहीं थी।</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>सिंधु घाटी सभ्यता</t>
+          <t>गाय उनके लिए पवित्र थी</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>उन्हें अश्वमेध का जानकारी थी</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता के बारे में कौन-सी उक्ति सही है ?</t>
+          <t xml:space="preserve">	हड़प्पावासी किस धातु से परिचित नहीं थे ?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>उन्होंने पशुपति का सम्मान करना आरंभ किया</t>
+          <t>लोहा</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>उनकी संस्कृति सामान्यतः स्थिर नहीं थी।</t>
+          <t>टीन एवं सीसा</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>गाय उनके लिए पवित्र थी</t>
+          <t>तांबा एवं कांसा</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>उन्हें अश्वमेध का जानकारी थी</t>
+          <t>सोना एवं चांदी</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>कपास का उत्पादन सर्वप्रथम सिन्धु क्षेत्र में हुआ, जिसे ग्रीक या यूनान के लोग किस नाम से पुकारा ?</t>
+          <t>किस हड़प्पाकालीन स्थल से प्राप्त जार पर चोंच में मछली दबाए चिड़िया एवं पेड़ के नीचे खड़ी लोमड़ी का चित्रांकन मिलता है, जो 'पंचतंत्र ' के लोमड़ी की कहानी सदृश्य है ?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>सिन्डन (Sindon)</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>रंगपुर</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>हड़प्पा</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>a' एवं 'b' दोनों</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>कॉटन (Cotton)</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>सिंधु घाटी सभ्यता के लोगों का मुख्य व्यवसाय क्या था ?</t>
+          <t>चन्हुदड़ो के उत्खनन का निर्देशन किया था -</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>व्यापार</t>
+          <t>जे. एच. मैके ने</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>पशुपालन</t>
+          <t>सर जॉन मार्शल ने</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>शिकार</t>
+          <t>आर. ई. एम. व्हीलर ने</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>कृषि</t>
+          <t>सर ऑरेल स्टीन ने</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा सभ्यता की खोज किस वर्ष में हुई थी ?</t>
+          <t xml:space="preserve">	हड़प्पा सभ्यता के अंतर्गत हल से जोते गये खेत का साक्ष्य कहाँ से मिला है ?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1921 ई०</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1935 ई०</t>
+          <t>रोपड़</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1901 ई०</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1942 ई०</t>
+          <t>अणावली</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा में एक उन्नत जल-प्रबंधन प्रणाली का पता चलता है</t>
+          <t>स्वातंत्र्योत्तर भारत में सबसे अधिक संख्या में हड़पायुगीन स्थलों की खोज किस प्रांत में हुई है?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>धौलावीरा में</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>कालीबंगन में</t>
+          <t>राजस्थान</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>आलमगीरपुर में</t>
+          <t>पंजाब और हरियाणा</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>लोथल में</t>
+          <t>उत्तर-पश्चिमी उत्तर प्रदेश</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>सिंधु घाटी के लोग विश्वास करते थे</t>
+          <t xml:space="preserve">	हड़प्पा एवं मोहनजोदड़ो की पुरातात्विक खुदाई के प्रभारी थे</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>मातृशक्ति में</t>
+          <t>सर जान मार्शल</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>यज्ञ प्रणाली में</t>
+          <t>कर्नल टाड</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>कर्मकाण्ड में</t>
+          <t>लाई क्लाइव</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>आत्मा और ब्रह्म में</t>
+          <t>लाई मैकाले</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>सिन्धु घाटी की सभ्यता के सन्दर्भ में निम्नलिखित कथनों पर विचार कीजिए - 1. यह प्रमुखत: लौकिक सभ्यता थी तथा उसमें धार्मिक तत्व, यद्यपि उपस्थित था, वर्चस्वशाली नहीं था | 2. उस काल में भारत में कपास से वस्त्र बनाये जाते थे | उपर्युक्त में से कौन-सा /कौन से कथन सही है/हैं ?</t>
+          <t>सिंधु घाटी की सभ्यता में घोड़े के अवशेष कहाँ मिले हैं ?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1 और 2 दोनों</t>
+          <t>सुरकोटदा</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>केवल 1</t>
+          <t>वणावली</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>केवल 2</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>न तो 1 और न ही 2</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>चन्हुदड़ो के उत्खनन का निर्देशन किया था -</t>
+          <t>किस पशु के अवशेष सिंधु घाटी सभ्यता में प्राप्त नहीं हुए हैं</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>जे. एच. मैके ने</t>
+          <t>शेर</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>सर जॉन मार्शल ने</t>
+          <t>घोड़ा</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>आर. ई. एम. व्हीलर ने</t>
+          <t>गाय</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>सर ऑरेल स्टीन ने</t>
+          <t>हाथी</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>किस हड़प्पाकालीन स्थल से ‘नृत्य मुद्रा वाली स्त्री की कांस्य मूर्ति' प्राप्त हुई है?</t>
+          <t>निम्नलिखित विद्वानों में से हड़प्पा सभ्यता का सर्वप्रथम खोजकर्ता कौन था ?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो से</t>
+          <t>दयाराम सहनी</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>कालीबंगा से</t>
+          <t>सर जॉन मार्शल</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>हड़प्पा से</t>
+          <t>आर० डी० बनर्जी</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>वणावली से</t>
+          <t>ए० कनिंघम</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता का कौन-सा स्थान भारत में स्थित है?</t>
+          <t>सिंधु सभ्यता के घर किससे बनाए जाते थे ?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>ईंट से</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>बांस से</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>पत्थर से</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>लकड़ी से</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (स्थल) A. हड़प्पा B. मोहनजोदड़ो C. लोथल D. कालीबंगा सूची-II (नदी) 1. रावी 2. सिंधु 3. भोगवा 4. घग्घर</t>
+          <t>सिंधु घाटी सभ्यता को खोज निकालने में जिन दो भारतीय का नाम जुड़ा है</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 3, D → 4</t>
+          <t>दयाराम साहनी एवं राखालदास बनर्जी</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>A → 2, B → 1, C → 4, D → 3</t>
+          <t>जान मार्शल एवं ईश्वरी प्रसाद</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>A → 4, B → 3, C → 2, D → 1</t>
+          <t>आशीर्वादीलाल श्रीवास्तव एवं रंगनाथ राव</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 4, D → 3</t>
+          <t>माधोस्वरूप वत्स एवं वी० बी० राव</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>सिंधु घाटी की सभ्यता निम्नलिखित में से किस सभ्यता के समकालीन नहीं थी ?</t>
+          <t>कौन-कौन से नगर सिंधु सभ्यता के बंदरगाह नगर थे ?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ग्रीक की सभ्यता</t>
+          <t>इनमें से सभी</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>मेसोपोटामिया की सभ्यता</t>
+          <t>कुनतासी</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>चीन की सभ्यता</t>
+          <t>अल्लाहदिनो एवं बालाकोट</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>मिस्र की सभ्यता</t>
+          <t>लोथल एवं सुत्कागेंडर</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>अफगानिस्तान स्थित सिंधु सभ्यता के स्थल हैं</t>
+          <t xml:space="preserve">	निम्नलिखित में से कौन-सी फसल हड़प्पाकालीन लोगों द्वारा उत्पादित नहीं की जाती थी?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(a) और (b) दोनों</t>
+          <t>दालें</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>चावल</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>सुर्तागोई</t>
+          <t>गेहूँ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>मुंडीगाक</t>
+          <t>जौ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>निम्नलिखित में कौन-सा सिंधु स्थल समुद्र तट पर स्थित नहीं था ?</t>
+          <t xml:space="preserve">	निम्नलिखित में से किस हड़प्पाकालीन स्थल से युगल शवाधान का साक्ष्य मिला है</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>कोटदीजी</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>बालाकोट</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>बणावली</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>सुरकोटदा</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>कथन (A) ; हड़प्पा तथा मोहनजोदड़ों अय विलुप्त हो गए हैं। कारण (R) : वे उत्खनन के दौरान प्रकट हुए थे।</t>
+          <t>सिंधु घाटी की सभ्यता निम्नलिखित में से किस सभ्यता के समकालीन नहीं थी ?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>A और R दोनों सही हैं तथा R, A का सही स्पष्टीकरण है</t>
+          <t>ग्रीक की सभ्यता</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>A और R दोनों सही हैं किन्तु R, A का सही स्पष्टीकरण नहीं है</t>
+          <t>मेसोपोटामिया की सभ्यता</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>A सही है किन्तु R गलत है</t>
+          <t>चीन की सभ्यता</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>A गलत है किन्तु R सही है</t>
+          <t>मिस्र की सभ्यता</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता के बारे में कौन-सा कथन असत्य है?</t>
+          <t>हड़प्पा के लोगों की सामाजिक पद्धति...... थी</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>लोग लोहे से परिचित थे</t>
+          <t>उचित समतावादी</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>मातृदेवी की उपासना की जाती थी</t>
+          <t>दास-श्रमिक आधारित</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>व्यापार और वाणिज्य उन्नत दशा में था</t>
+          <t>वर्ण आधारित</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>नगरों में नालियों की सुदृढ़ व्यवस्था थी</t>
+          <t>जाति आधारित</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता के घर किससे बनाए जाते थे ?</t>
+          <t xml:space="preserve">	सूची-I को सूची-II से सुमेलित कीजिए : सूची-I A. सिंधु सभ्यता की उत्तरी सीमा B. सिंधु सभ्यता की दक्षिणी सीमा C. सिंधु सभ्यता की पूर्वी सीमा D. सिंधु सभ्यता की पश्चिमी सीमा सूची-II 1. माडा/जम्मू 2. दैमाबाद/महाराष्ट्र 3. आलमगीरपुर / उत्तर प्रदेश 4. सुत्कागेंडर/बलूचिस्तान</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ईंट से</t>
+          <t>A → 1, B → 2, C → 3, D → 4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>बांस से</t>
+          <t>A → 2, B → 1, C → 4, D → 3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>पत्थर से</t>
+          <t>A → 4, B → 3, C → 2, D → 1</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>लकड़ी से</t>
+          <t>A → 1, B → 2, C → 4, D → 3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>हड़प्पाकालीन स्थलों में अभी तक किस धातु की प्राप्ति नहीं हुई है ?</t>
+          <t>हड़प्पा सभ्यता के सम्पूर्ण क्षेत्र का आकार किस प्रकार का था ?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>लोहा</t>
+          <t>त्रिभुजाकार</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>चांदी</t>
+          <t>गोलाकार</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>स्वर्ण</t>
+          <t>आयताकार</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>तांबा</t>
+          <t>वर्गाकार</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>भारत में खोजा गया सबसे पहला पुराना शहर था</t>
+          <t xml:space="preserve">	सिंधु घाटी सभ्यता जानी जाती है।</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>अपने नगर नियोजन के लिए</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>मोहनजोदड़ो एवं हड़प्पा के लिए</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>अपने कृषि संबंधी कार्यों के लिए</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>सिंध</t>
+          <t>अपने उद्योगों के लिए</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>हड़प्पा के मिट्टी के बर्तनों पर सामान्यतः किस रंग का उपयोग हुआ था?</t>
+          <t>सिंधु घाटी स्थल कालीबंगन किस प्रदेश में है ?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>लाल</t>
+          <t>राजस्थान में</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>नीला-हरा</t>
+          <t>गुजरात में</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>पांडु</t>
+          <t>मध्य प्रदेश में</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>नीला</t>
+          <t>उत्तर प्रदेश में</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>हड़प्पावासी लाजवर्द-Lapislazuli- (भवन निर्माण की सामग्री) का आयात कहाँ से करते थे ?</t>
+          <t>हड़प्पा सभ्यता की खोज किस वर्ष में हुई थी ?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>हिन्दूकुश क्षेत्र के बदख्शा से</t>
+          <t>1921 ई०</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ईरान से</t>
+          <t>1901 ई०</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>दक्षिण भारत से</t>
+          <t>1942 ई०</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>बलूचिस्तान से</t>
+          <t>1935 ई०</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>निम्नलिखित में से कौन-सा हड़प्पाकालीन स्थल गुजरात में था ?</t>
+          <t>सिंधु सभ्यता के बारे में कौन-सा कथन असत्य है?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>लोग लोहे से परिचित थे</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>वणावली</t>
+          <t>मातृदेवी की उपासना की जाती थी</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>रोपड़</t>
+          <t>व्यापार और वाणिज्य उन्नत दशा में था</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>नगरों में नालियों की सुदृढ़ व्यवस्था थी</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>हड़प्पावासी किस वस्तु के उत्पादन में सर्वप्रथम थे</t>
+          <t>सिंधु सभ्यता का पत्तननगर (बंदरगाह) कौन-सा था ?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>कपास</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>मुद्राएँ</t>
+          <t>रोपड़</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>कांसे के औजार</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>जौ</t>
+          <t>कालीबंगन</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (हडप्पीय स्थल) A. मांडा B. दायमाबाद C. कालीबंगा D. राखीगढ़ी सूची-II (स्थिति) 1. राजस्थान 2. हरियाणा 3. जम्मू-कश्मीर 4. महाराष्ट्र</t>
+          <t>सिंधु सभ्यता का कौन-सा स्थान भारत में स्थित है?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>A → 3, B → 4, C → 1, D → 2</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>A → 4, B → 1, C → 2, D → 3</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>A → 2, B → 3, C → 4, D → 1</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 3, D → 4</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>किस हड़प्पाकालीन स्थल से प्राप्त जार पर चोंच में मछली दबाए चिड़िया एवं पेड़ के नीचे खड़ी लोमड़ी का चित्रांकन मिलता है, जो 'पंचतंत्र ' के लोमड़ी की कहानी सदृश्य है ?</t>
+          <t>कथन (A) ; हड़प्पा तथा मोहनजोदड़ों अय विलुप्त हो गए हैं। कारण (R) : वे उत्खनन के दौरान प्रकट हुए थे।</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>A और R दोनों सही हैं तथा R, A का सही स्पष्टीकरण है</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>रंगपुर</t>
+          <t>A और R दोनों सही हैं किन्तु R, A का सही स्पष्टीकरण नहीं है</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>A सही है किन्तु R गलत है</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>A गलत है किन्तु R सही है</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>किस हड़प्पाकालीन स्थल से ‘पुजारी की प्रस्तर मूर्ति प्राप्त हुई है?</t>
+          <t>हड़प्पाकालीन स्थल रोपड़/ पंजाव किस नदी के किनारे स्थित था ?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>सतलज</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>चेनाब</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>रंगपुर</t>
+          <t>सिंधु</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>रावी</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>निम्नलिखित में से किस पदार्थ का उपयोग हड़प्पा काल की मुद्राओं के निर्माण में मुख्य रूप से किया गया था ?</t>
+          <t>सिन्धु सभ्यता निम्नलिखित में से किस युग में पड़ता है?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>सेलखड़ी (steatite)</t>
+          <t>आद्य ऐतिहासिक काल (Proto-Historical Period)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>कांसा</t>
+          <t>उत्तर-प्रागैतिहासिक काल (Post-Historical Period)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ताँवा</t>
+          <t>प्रागतिहासिक काल (Pre-Historical Period)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>लोहा</t>
+          <t>ऐतिहासिक काल (Historical Period)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">	सूची-I को सूची-II से सुमेलित कीजिए : सूची-I A. सिंधु सभ्यता की उत्तरी सीमा B. सिंधु सभ्यता की दक्षिणी सीमा C. सिंधु सभ्यता की पूर्वी सीमा D. सिंधु सभ्यता की पश्चिमी सीमा सूची-II 1. माडा/जम्मू 2. दैमाबाद/महाराष्ट्र 3. आलमगीरपुर / उत्तर प्रदेश 4. सुत्कागेंडर/बलूचिस्तान</t>
+          <t>सिंधु सभ्यता का सर्वाधिक उपयुक्त नाम क्या है?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 3, D → 4</t>
+          <t>हड़प्पा सभ्यता</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>A → 2, B → 1, C → 4, D → 3</t>
+          <t>सिंधु सभ्यता</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>A → 4, B → 3, C → 2, D → 1</t>
+          <t>सिंधु घाटी सभ्यता</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 4, D → 3</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>निम्न में से कौन से लक्षण सभ्यता के लोगों का सही चित्रण करता हैं 1. उनके विशाल महल और मन्दिर होते थे 2. वे देवियों और देवताओं दोनों की पूजा करते थे l 3. वे युद्ध में घोड़ों द्वारा खींचे जानेवाले रथों का प्रयोग करते थे नीचे दिए गये कूट का प्रयोग कर सही कथन को चुनिए</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>2</v>
+          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (हडप्पीय स्थल) A. मांडा B. दायमाबाद C. कालीबंगा D. राखीगढ़ी सूची-II (स्थिति) 1. राजस्थान 2. हरियाणा 3. जम्मू-कश्मीर 4. महाराष्ट्र</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>A → 3, B → 4, C → 1, D → 2</t>
+        </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>A → 4, B → 1, C → 2, D → 3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1,2,3</t>
+          <t>A → 2, B → 3, C → 4, D → 1</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>A → 1, B → 2, C → 3, D → 4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>हड़प्पा के लोगों की सामाजिक पद्धति...... थी</t>
+          <t>कपास का उत्पादन सर्वप्रथम सिन्धु क्षेत्र में हुआ, जिसे ग्रीक या यूनान के लोग किस नाम से पुकारा ?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>उचित समतावादी</t>
+          <t>सिन्डन (Sindon)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>दास-श्रमिक आधारित</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>वर्ण आधारित</t>
+          <t>a' एवं 'b' दोनों</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>जाति आधारित</t>
+          <t>कॉटन (Cotton)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>कौन-कौन से नगर सिंधु सभ्यता के बंदरगाह नगर थे ?</t>
+          <t>मोहनजोदड़ो को किस एक अन्य नाम से भी जाना जाता है ?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>इनमें से सभी</t>
+          <t>मृतकों का टीला (Mound of Dead)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>कुनतासी</t>
+          <t>दासों का टीला (Mound of Slaves)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>अल्लाहदिनो एवं बालाकोट</t>
+          <t>कंकालों का टीला (Mound of Skeletons)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>लोथल एवं सुत्कागेंडर</t>
+          <t>जीवितों का टीला (Mound of Living)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>निम्नलिखित विद्वानों में से हड़प्पा सभ्यता का सर्वप्रथम खोजकर्ता कौन था ?</t>
+          <t>सिंधु घाटी सभ्यता के लोगों का मुख्य व्यवसाय क्या था ?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>दयाराम सहनी</t>
+          <t>व्यापार</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>सर जॉन मार्शल</t>
+          <t>पशुपालन</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>आर० डी० बनर्जी</t>
+          <t>शिकार</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ए० कनिंघम</t>
+          <t>कृषि</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>निम्न में से किस पशु की आकृति जो मुहर पर मिली है, जिससे ज्ञात होता है, कि सिंधु घाटी एवं मेसोपोटामिया की सभ्यताओं के मध्य व्यापारिक संबंध थे</t>
+          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (प्राचीन स्थल) A. लोथल B. कालीबंगन C. धौलावीर D. बनवाली सूची-II (पुरातत्वीय अवशेष) 1. जूता हुआ खेत 2. गोदीबाड़ा (Dockyaard) 3. पकी मिट्टी की बनी हुई हल की प्रतिकृति 4. हड़प्पाई लिपि के बड़े आकार के दस चिन्हों वाला एक शिलालेख</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>बैल</t>
+          <t>A → 2, B → 1, C → 4, D → 3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>गधा</t>
+          <t>A → 3, B → 1, C → 4, D → 2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>हाथी</t>
+          <t>A → 1, B → 2, C → 4, D → 3</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>घोड़ा</t>
+          <t>A → 1, B → 2, C → 3, D → 4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा सभ्यता के अंतर्गत हल से जोते गये खेत का साक्ष्य कहाँ से मिला है ?</t>
+          <t>हड़प्पा सभ्यता का सर्वाधिक मान्यता प्राप्त काल है</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>2500 ई०पू०-1750 ई०पू०</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>रोपड़</t>
+          <t>2800 ई०पू०-2000 ई०पू०</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>3500 ई०पू०-1800 ई०पू०</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>अणावली</t>
+          <t>निश्चित नहीं हो सका है</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा सभ्यता किस युग की थी ?</t>
+          <t>हड़प्पा सभ्यता का प्रचलित नाम है।</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>कांस्य युग</t>
+          <t>मोहनजोदड़ो की सभ्यता</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>नवपाषाण युग</t>
+          <t>सिन्धु घाटी की सभ्यता</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>पुरापाषाण युग</t>
+          <t>लोथल सभ्यता</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>लौह युग</t>
+          <t>सिंधु सभ्यता</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>सिंधु घाटी सभ्यता की विकसित अवस्था में निम्नलिखित में से किस स्थल में घरों में कुँओं के अवशेष मिले हैं?</t>
+          <t>अफगानिस्तान स्थित सिंधु सभ्यता के स्थल हैं</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>(a) और (b) दोनों</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>सुर्तागोई</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>हडपा</t>
+          <t>मुंडीगाक</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो को किस एक अन्य नाम से भी जाना जाता है ?</t>
+          <t>सिंधु घाटी सभ्यता की विकसित अवस्था में निम्नलिखित में से किस स्थल में घरों में कुँओं के अवशेष मिले हैं?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>मृतकों का टीला (Mound of Dead)</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>दासों का टीला (Mound of Slaves)</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>कंकालों का टीला (Mound of Skeletons)</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>जीवितों का टीला (Mound of Living)</t>
+          <t>हडपा</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>सिंधु घाटी की सभ्यता में घोड़े के अवशेष कहाँ मिले हैं ?</t>
+          <t>सैंधव स्थलों के उत्खनन से प्राप्त मुहरों पर निम्नलिखित में से किस पशु का सर्वाधिक उत्कीर्णन हुआ है ?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>सुरकोटदा</t>
+          <t>बैल</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>वणावली</t>
+          <t>हाथी</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>घोड़ा</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>शेर</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>सिंधु घाटी स्थल कालीबंगन किस प्रदेश में है ?</t>
+          <t>भारत में खोजा गया सबसे पहला पुराना शहर था</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>राजस्थान में</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>गुजरात में</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>मध्य प्रदेश में</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश में</t>
+          <t>सिंध</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>हड़प्पावासी किन-किन धातुओं का आयात करते थे ? उत्तर कूट में दें - कूट : 1. चाँदी 2. टिन 3. सोना</t>
+          <t xml:space="preserve">	हड़प्पा सभ्यता किस युग की थी ?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1, 2 एवं 3</t>
+          <t>कांस्य युग</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1 एवं 2</t>
+          <t>नवपाषाण युग</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1 एवं 3</t>
+          <t>पुरापाषाण युग</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2 एवं 3</t>
+          <t>लौह युग</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>हड़प्पाकालीन स्थल रोपड़/ पंजाव किस नदी के किनारे स्थित था ?</t>
+          <t xml:space="preserve">	हड़प्पाकालीन समाज किन वर्गों में विभक्त था ?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>सतलज</t>
+          <t>विद्वान, योद्धा, व्यापारी और श्रमिक</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>चेनाब</t>
+          <t>शिकारी, पुजारी, किसान और क्षत्रिय</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>सिंधु</t>
+          <t>ब्राह्मण, क्षत्रिय, वैश्य और शूद्र</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>रावी</t>
+          <t>राजा, पुरोहित, सैनिक और शूद्र</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>किस पशु के अवशेष सिंधु घाटी सभ्यता में प्राप्त नहीं हुए हैं</t>
+          <t>हड़प्पा सभ्यता के निवासी थे</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>शेर</t>
+          <t>शहरी</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>घोड़ा</t>
+          <t>ग्रामीण</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>गाय</t>
+          <t>यायावर / खानाबदोश</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>हाथी</t>
+          <t>जनजातीय</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>सिंधु घाटी सभ्यता को खोज निकालने में जिन दो भारतीय का नाम जुड़ा है</t>
+          <t>निम्नलिखित में से कौन-सा हड़प्पाकालीन स्थल गुजरात में था ?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>दयाराम साहनी एवं राखालदास बनर्जी</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>जान मार्शल एवं ईश्वरी प्रसाद</t>
+          <t>वणावली</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>आशीर्वादीलाल श्रीवास्तव एवं रंगनाथ राव</t>
+          <t>रोपड़</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>माधोस्वरूप वत्स एवं वी० बी० राव</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (प्राचीन स्थल) A. लोथल B. कालीबंगन C. धौलावीर D. बनवाली सूची-II (पुरातत्वीय अवशेष) 1. जूता हुआ खेत 2. गोदीबाड़ा (Dockyaard) 3. पकी मिट्टी की बनी हुई हल की प्रतिकृति 4. हड़प्पाई लिपि के बड़े आकार के दस चिन्हों वाला एक शिलालेख</t>
+          <t>किस सिंधुकालीन स्थल से एक ईट पर बिल्ली का पीछा करते हुए कुत्ते के पंजों के निशान मिले हैं ?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>A → 2, B → 1, C → 4, D → 3</t>
+          <t>चन्हुदड़ो</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>A → 3, B → 1, C → 4, D → 2</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 4, D → 3</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 3, D → 4</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>सैंधव स्थलों के उत्खनन से प्राप्त मुहरों पर निम्नलिखित में से किस पशु का सर्वाधिक उत्कीर्णन हुआ है ?</t>
+          <t>सिंधु घाटी के लोग विश्वास करते थे</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>बैल</t>
+          <t>मातृशक्ति में</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>हाथी</t>
+          <t>यज्ञ प्रणाली में</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>घोड़ा</t>
+          <t>कर्मकाण्ड में</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>शेर</t>
+          <t>आत्मा और ब्रह्म में</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो से प्राप्त पशुपति शिव/ आद्य शिव मुहर में किन किन जानवरों का अंकन हुआ है ?</t>
+          <t>सैंधव सभ्यता की ईटों का अलंकरण किस स्थान से मिला है?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>इनमें से सभी</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>हिरण</t>
+          <t>चन्हूदड़ो</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>गैंडा एवं भैंसा</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>व्याघ्र एवं हाथी</t>
+          <t>बणावली</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>सैंधव सभ्यता की ईटों का अलंकरण किस स्थान से मिला है?</t>
+          <t>हड़प्पा के मिट्टी के बर्तनों पर सामान्यतः किस रंग का उपयोग हुआ था?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>लाल</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>चन्हूदड़ो</t>
+          <t>नीला-हरा</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>पांडु</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>बणावली</t>
+          <t>नीला</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">	मोहनजोदड़ो कहाँ स्थित है?</t>
+          <t xml:space="preserve">	रंगपुर जहाँ हड़प्पा की समकालीन सभ्यता थी, है -</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>सिंध</t>
+          <t>सौराष्ट्र में</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>राजस्थान में</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश</t>
+          <t>उत्तर प्रदेश में</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>पंजाब में</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>मांडा किस नदी के किनारे स्थित था?</t>
+          <t>मोहनजोदड़ो से प्राप्त पशुपति शिव/ आद्य शिव मुहर में किन किन जानवरों का अंकन हुआ है ?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>चेनाब</t>
+          <t>इनमें से सभी</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>सतलज</t>
+          <t>हिरण</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>रावी</t>
+          <t>गैंडा एवं भैंसा</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>सिंधु</t>
+          <t>व्याघ्र एवं हाथी</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>स्वातंत्र्योत्तर भारत में सबसे अधिक संख्या में हड़पायुगीन स्थलों की खोज किस प्रांत में हुई है?</t>
+          <t>सिंधु सभ्यता की मुद्रा में किस देवता के रामतुल्य चित्रांकन मिलता है</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>आद्य शिव</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>राजस्थान</t>
+          <t>आद्य ब्रह्मा</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>पंजाब और हरियाणा</t>
+          <t>अद्य विष्णु</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>उत्तर-पश्चिमी उत्तर प्रदेश</t>
+          <t>आद्य इन्द्र</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पावासी किस धातु से परिचित नहीं थे ?</t>
+          <t>हड़प्पाकालीन स्थलों में अभी तक किस धातु की प्राप्ति नहीं हुई है ?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2895,48 +2895,48 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>टीन एवं सीसा</t>
+          <t>चांदी</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>तांबा एवं कांसा</t>
+          <t>स्वर्ण</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>सोना एवं चांदी</t>
+          <t>तांबा</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>सिन्धु सभ्यता निम्नलिखित में से किस युग में पड़ता है?</t>
+          <t>मांडा किस नदी के किनारे स्थित था?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>आद्य ऐतिहासिक काल (Proto-Historical Period)</t>
+          <t>चेनाब</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>उत्तर-प्रागैतिहासिक काल (Post-Historical Period)</t>
+          <t>सतलज</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>प्रागतिहासिक काल (Pre-Historical Period)</t>
+          <t>रावी</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ऐतिहासिक काल (Historical Period)</t>
+          <t>सिंधु</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>

--- a/Data/indus.xlsx
+++ b/Data/indus.xlsx
@@ -467,2476 +467,2476 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>निम्नलिखित में कौन-सा सिंधु स्थल समुद्र तट पर स्थित नहीं था ?</t>
+          <t>सिंधु सभ्यता का सर्वाधिक उपयुक्त नाम क्या है?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>कोटदीजी</t>
+          <t>हड़प्पा सभ्यता</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>बालाकोट</t>
+          <t>सिंधु सभ्यता</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>सिंधु घाटी सभ्यता</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>सुरकोटदा</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>निम्न में से कौन से लक्षण सभ्यता के लोगों का सही चित्रण करता हैं 1. उनके विशाल महल और मन्दिर होते थे 2. वे देवियों और देवताओं दोनों की पूजा करते थे l 3. वे युद्ध में घोड़ों द्वारा खींचे जानेवाले रथों का प्रयोग करते थे नीचे दिए गये कूट का प्रयोग कर सही कथन को चुनिए</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
+          <t>हड़प्पा के लोगों की सामाजिक पद्धति...... थी</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>उचित समतावादी</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>दास-श्रमिक आधारित</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1,2,3</t>
+          <t>जाति आधारित</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>वर्ण आधारित</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>किस हड़प्पाकालीन स्थल से ‘पुजारी की प्रस्तर मूर्ति प्राप्त हुई है?</t>
+          <t>निम्नलिखित में से किस पदार्थ का उपयोग हड़प्पा काल की मुद्राओं के निर्माण में मुख्य रूप से किया गया था ?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>सेलखड़ी (steatite)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>कांसा</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>रंगपुर</t>
+          <t>ताँवा</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>लोहा</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>भारत में चाँदी की उपलब्धता के प्राचीनतम साक्ष्य मिलते हैं</t>
+          <t>निम्नलिखित पशुओं में से किस एक का हड़प्पा सभ्यता में पाई मुहरों और टेराकोटा कलाकृतियों में निरूपण / अंकन नहीं हुआ था ?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>हड़प्पा संस्कृति में</t>
+          <t>शेर</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>पश्चिमी भारत की ताम्रपाषाण संस्कृति में</t>
+          <t>हाथी</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>वैदिक संहिताओं में</t>
+          <t>गैंडा</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>चॉदी के आहत मुद्राओं में</t>
+          <t>बाघ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>सिन्धु घाटी की सभ्यता के सन्दर्भ में निम्नलिखित कथनों पर विचार कीजिए - 1. यह प्रमुखत: लौकिक सभ्यता थी तथा उसमें धार्मिक तत्व, यद्यपि उपस्थित था, वर्चस्वशाली नहीं था | 2. उस काल में भारत में कपास से वस्त्र बनाये जाते थे | उपर्युक्त में से कौन-सा /कौन से कथन सही है/हैं ?</t>
+          <t>हड़प्पाकालीन स्थलों में अभी तक किस धातु की प्राप्ति नहीं हुई है ?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1 और 2 दोनों</t>
+          <t>लोहा</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>केवल 1</t>
+          <t>चांदी</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>केवल 2</t>
+          <t>स्वर्ण</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>न तो 1 और न ही 2</t>
+          <t>तांबा</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>सिंध का नखलिस्तान / बाग' हड़प्पा सभ्यता के किस पुरास्थल को कहा गया?</t>
+          <t xml:space="preserve">	निम्नलिखित में से किस हड़प्पाकालीन स्थल से युगल शवाधान का साक्ष्य मिला है</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>लोथल</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>कालीबंगा</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>बणावली</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>हड़प्पा</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>मोहनजोदड़ो</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>कालीबंगा</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>लोथल</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>निम्न में से कौन से लक्षण सभ्यता के लोगों का सही चित्रण करता हैं 1. उनके विशाल महल और मन्दिर होते थे 2. वे देवियों और देवताओं दोनों की पूजा करते थे l 3. वे युद्ध में घोड़ों द्वारा खींचे जानेवाले रथों का प्रयोग करते थे नीचे दिए गये कूट का प्रयोग कर सही कथन को चुनिए</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
+          <t>सैंधव स्थलों के उत्खनन से प्राप्त मुहरों पर निम्नलिखित में से किस पशु का सर्वाधिक उत्कीर्णन हुआ है ?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>बैल</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>हाथी</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1,2,3</t>
+          <t>घोड़ा</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>शेर</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>पैमानों की खोज ने यह सिद्ध कर दिया है कि सिंधु घाटी के लोग माप और तौल से परिचित थे। यह खोज कहाँ पर हुई ?</t>
+          <t>सिंधु सभ्यता की मुद्रा में किस देवता के रामतुल्य चित्रांकन मिलता है</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>आद्य शिव</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>कालीबंगन</t>
+          <t>आद्य ब्रह्मा</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>अद्य विष्णु</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>चहुदड़ी</t>
+          <t>आद्य इन्द्र</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">	मोहनजोदड़ो कहाँ स्थित है?</t>
+          <t>मोहनजोदड़ो से प्राप्त पशुपति शिव/ आद्य शिव मुहर में किन किन जानवरों का अंकन हुआ है ?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>सिंध</t>
+          <t>इनमें से सभी</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>हिरण</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश</t>
+          <t>गैंडा एवं भैंसा</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>व्याघ्र एवं हाथी</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा सभ्यता की खोज किस वर्ष में हुई थी ?</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1921 ई०</t>
-        </is>
+          <t>निम्न में से कौन से लक्षण सभ्यता के लोगों का सही चित्रण करता हैं 1. उनके विशाल महल और मन्दिर होते थे 2. वे देवियों और देवताओं दोनों की पूजा करते थे l 3. वे युद्ध में घोड़ों द्वारा खींचे जानेवाले रथों का प्रयोग करते थे नीचे दिए गये कूट का प्रयोग कर सही कथन को चुनिए</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1935 ई०</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1901 ई०</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1942 ई०</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा में एक उन्नत जल-प्रबंधन प्रणाली का पता चलता है</t>
+          <t>मांडा किस नदी के किनारे स्थित था?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>धौलावीरा में</t>
+          <t>चेनाब</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>कालीबंगन में</t>
+          <t>सतलज</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>आलमगीरपुर में</t>
+          <t>रावी</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>लोथल में</t>
+          <t>सिंधु</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा के काल का ताँबे का रथ किस स्थान से प्राप्त हुआ है ?</t>
+          <t>हड़प्पा सभ्यता के बारे में कौन-सी उक्ति सही है ?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>दैमावाद</t>
+          <t>उन्होंने पशुपति का सम्मान करना आरंभ किया</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>बणावली</t>
+          <t>उनकी संस्कृति सामान्यतः स्थिर नहीं थी।</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>कुणाल</t>
+          <t>गाय उनके लिए पवित्र थी</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>राखीगढ़ी</t>
+          <t>उन्हें अश्वमेध का जानकारी थी</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (स्थल) A. हड़प्पा B. मोहनजोदड़ो C. लोथल D. कालीबंगा सूची-II (नदी) 1. रावी 2. सिंधु 3. भोगवा 4. घग्घर</t>
+          <t>अफगानिस्तान स्थित सिंधु सभ्यता के स्थल हैं</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 3, D → 4</t>
+          <t>(a) और (b) दोनों</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A → 2, B → 1, C → 4, D → 3</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A → 4, B → 3, C → 2, D → 1</t>
+          <t>सुर्तागोई</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 4, D → 3</t>
+          <t>मुंडीगाक</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>हड़प्पावासी किन-किन धातुओं का आयात करते थे ? उत्तर कूट में दें - कूट : 1. चाँदी 2. टिन 3. सोना</t>
+          <t>कपास का उत्पादन सर्वप्रथम सिन्धु क्षेत्र में हुआ, जिसे ग्रीक या यूनान के लोग किस नाम से पुकारा ?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1, 2 एवं 3</t>
+          <t>सिन्डन (Sindon)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1 एवं 2</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1 एवं 3</t>
+          <t>a' एवं 'b' दोनों</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2 एवं 3</t>
+          <t>कॉटन (Cotton)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>किस हड़प्पाकालीन स्थल से ‘नृत्य मुद्रा वाली स्त्री की कांस्य मूर्ति' प्राप्त हुई है?</t>
+          <t xml:space="preserve">	हड़प्पा एवं मोहनजोदड़ो की पुरातात्विक खुदाई के प्रभारी थे</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो से</t>
+          <t>सर जान मार्शल</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>कालीबंगा से</t>
+          <t>कर्नल टाड</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>हड़प्पा से</t>
+          <t>लाई क्लाइव</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>वणावली से</t>
+          <t>लाई मैकाले</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">	सिंधु सभ्यता में वृहत् स्नानागार पाया गया है</t>
+          <t>सिंधु घाटी की सभ्यता में घोड़े के अवशेष कहाँ मिले हैं ?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो में</t>
+          <t>सुरकोटदा</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>हड़प्पा में</t>
+          <t>वणावली</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>लोथल में</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>कालीबंगा में</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>निम्न में से किस पशु की आकृति जो मुहर पर मिली है, जिससे ज्ञात होता है, कि सिंधु घाटी एवं मेसोपोटामिया की सभ्यताओं के मध्य व्यापारिक संबंध थे</t>
+          <t>भारत में चाँदी की उपलब्धता के प्राचीनतम साक्ष्य मिलते हैं</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>बैल</t>
+          <t>हड़प्पा संस्कृति में</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>गधा</t>
+          <t>पश्चिमी भारत की ताम्रपाषाण संस्कृति में</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>हाथी</t>
+          <t>वैदिक संहिताओं में</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>घोड़ा</t>
+          <t>चॉदी के आहत मुद्राओं में</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>हड़प्पाकालीन लोगों ने नगरों में घरों के विन्यास के लिए कौन-सी पद्धति अपनायी - थी ?</t>
+          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (हडप्पीय स्थल) A. मांडा B. दायमाबाद C. कालीबंगा D. राखीगढ़ी सूची-II (स्थिति) 1. राजस्थान 2. हरियाणा 3. जम्मू-कश्मीर 4. महाराष्ट्र</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ग्रीड पद्धति में</t>
+          <t>A → 3, B → 4, C → 1, D → 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>त्रिभुजाकार आकृति में</t>
+          <t>A → 4, B → 1, C → 2, D → 3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>गोलाकार आकृति में</t>
+          <t>A → 2, B → 3, C → 4, D → 1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>कमल पुष्प की आकृति का</t>
+          <t>A → 1, B → 2, C → 3, D → 4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>निम्नलिखित पशुओं में से किस एक का हड़प्पा सभ्यता में पाई मुहरों और टेराकोटा कलाकृतियों में निरूपण / अंकन नहीं हुआ था ?</t>
+          <t>निम्नलिखित में से कौन-सा हड़प्पाकालीन स्थल गुजरात में था ?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>शेर</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>हाथी</t>
+          <t>वणावली</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>गैंडा</t>
+          <t>रोपड़</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>बाघ</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">	सिंधु घाटी की सभ्यता कहाँ तक विस्तृत थी?</t>
+          <t xml:space="preserve">	‘सिंध का नखलिस्तान / बाग' हड़प्पा सभ्यता के किस पुरास्थल को कहा गया?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>पंजाब, राजस्थान, गुजरात, उत्तर प्रदेश, हरियाणा, सिंध और बलुचिस्तान</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>जाब, राजस्थान, गुजरात, उड़ीसा और बंगाल</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>राजस्थान, बिहार, बंगाल और उड़ीसा</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>पंजाब, दिल्ली और जम्मू-कश्मीर</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>हड़प्पावासी लाजवर्द-Lapislazuli- (भवन निर्माण की सामग्री) का आयात कहाँ से करते थे ?</t>
+          <t>सिन्धु घाटी की सभ्यता के सन्दर्भ में निम्नलिखित कथनों पर विचार कीजिए - 1. यह प्रमुखत: लौकिक सभ्यता थी तथा उसमें धार्मिक तत्व, यद्यपि उपस्थित था, वर्चस्वशाली नहीं था | 2. उस काल में भारत में कपास से वस्त्र बनाये जाते थे | उपर्युक्त में से कौन-सा /कौन से कथन सही है/हैं ?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>हिन्दूकुश क्षेत्र के बदख्शा से</t>
+          <t>1 और 2 दोनों</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ईरान से</t>
+          <t>केवल 1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>दक्षिण भारत से</t>
+          <t>केवल 2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>बलूचिस्तान से</t>
+          <t>न तो 1 और न ही 2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता के बारे में कौन-सी उक्ति सही है ?</t>
+          <t>किस हड़प्पाकालीन स्थल से ‘नृत्य मुद्रा वाली स्त्री की कांस्य मूर्ति' प्राप्त हुई है?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>उन्होंने पशुपति का सम्मान करना आरंभ किया</t>
+          <t>मोहनजोदड़ो से</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>उनकी संस्कृति सामान्यतः स्थिर नहीं थी।</t>
+          <t>कालीबंगा से</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>गाय उनके लिए पवित्र थी</t>
+          <t>हड़प्पा से</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>उन्हें अश्वमेध का जानकारी थी</t>
+          <t>वणावली से</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>निम्नलिखित में से कौन मोहनजोदड़ो की सबसे बड़ी इमारत मानी जाती है?</t>
+          <t>हड़प्पावासी किस वस्तु के उत्पादन में सर्वप्रथम थे</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>विशाल अन्नागार / धान्यकोठार</t>
+          <t>कपास</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>विशाल स्नानागार</t>
+          <t>मुद्राएँ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>कांसे के औजार</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>सभा भवन</t>
+          <t>जौ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>हड़प्पावासी किस वस्तु के उत्पादन में सर्वप्रथम थे</t>
+          <t xml:space="preserve">	हड़प्पाकालीन समाज किन वर्गों में विभक्त था ?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>कपास</t>
+          <t>विद्वान, योद्धा, व्यापारी और श्रमिक</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>मुद्राएँ</t>
+          <t>शिकारी, पुजारी, किसान और क्षत्रिय</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>कांसे के औजार</t>
+          <t>ब्राह्मण, क्षत्रिय, वैश्य और शूद्र</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>जौ</t>
+          <t>राजा, पुरोहित, सैनिक और शूद्र</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>निम्नलिखित में से किस पदार्थ का उपयोग हड़प्पा काल की मुद्राओं के निर्माण में मुख्य रूप से किया गया था ?</t>
+          <t>सिंधु घाटी के लोग विश्वास करते थे</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>सेलखड़ी (steatite)</t>
+          <t>मातृशक्ति में</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>कांसा</t>
+          <t>यज्ञ प्रणाली में</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ताँवा</t>
+          <t>कर्मकाण्ड में</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>लोहा</t>
+          <t>आत्मा और ब्रह्म में</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">	‘सिंध का नखलिस्तान / बाग' हड़प्पा सभ्यता के किस पुरास्थल को कहा गया?</t>
+          <t>हड़प्पा सभ्यता की खोज किस वर्ष में हुई थी ?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>1921 ई०</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>1901 ई०</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>1942 ई०</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>1935 ई०</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>हड़प्पा के लोगों की सामाजिक पद्धति...... थी</t>
+          <t>हड़प्पा सभ्यता के निवासी थे</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>उचित समतावादी</t>
+          <t>शहरी</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>दास-श्रमिक आधारित</t>
+          <t>ग्रामीण</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>जाति आधारित</t>
+          <t>यायावर / खानाबदोश</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>वर्ण आधारित</t>
+          <t>जनजातीय</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता के बारे में कौन-सी उक्ति सही है ?</t>
+          <t xml:space="preserve">	हड़प्पा सभ्यता के अंतर्गत हल से जोते गये खेत का साक्ष्य कहाँ से मिला है ?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>उन्होंने पशुपति का सम्मान करना आरंभ किया</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>उनकी संस्कृति सामान्यतः स्थिर नहीं थी।</t>
+          <t>रोपड़</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>गाय उनके लिए पवित्र थी</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>उन्हें अश्वमेध का जानकारी थी</t>
+          <t>अणावली</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पावासी किस धातु से परिचित नहीं थे ?</t>
+          <t>सैंधव सभ्यता की ईटों का अलंकरण किस स्थान से मिला है?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>लोहा</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>टीन एवं सीसा</t>
+          <t>चन्हूदड़ो</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>तांबा एवं कांसा</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>सोना एवं चांदी</t>
+          <t>बणावली</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>किस हड़प्पाकालीन स्थल से प्राप्त जार पर चोंच में मछली दबाए चिड़िया एवं पेड़ के नीचे खड़ी लोमड़ी का चित्रांकन मिलता है, जो 'पंचतंत्र ' के लोमड़ी की कहानी सदृश्य है ?</t>
+          <t xml:space="preserve">	निम्नलिखित में से कौन-सी फसल हड़प्पाकालीन लोगों द्वारा उत्पादित नहीं की जाती थी?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>दालें</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>रंगपुर</t>
+          <t>चावल</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>गेहूँ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>जौ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>चन्हुदड़ो के उत्खनन का निर्देशन किया था -</t>
+          <t>सिंधु घाटी की सभ्यता निम्नलिखित में से किस सभ्यता के समकालीन नहीं थी ?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>जे. एच. मैके ने</t>
+          <t>ग्रीक की सभ्यता</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>सर जॉन मार्शल ने</t>
+          <t>मेसोपोटामिया की सभ्यता</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>आर. ई. एम. व्हीलर ने</t>
+          <t>चीन की सभ्यता</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>सर ऑरेल स्टीन ने</t>
+          <t>मिस्र की सभ्यता</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा सभ्यता के अंतर्गत हल से जोते गये खेत का साक्ष्य कहाँ से मिला है ?</t>
+          <t>हड़प्पाकालीन स्थल रोपड़/ पंजाव किस नदी के किनारे स्थित था ?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>सतलज</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>रोपड़</t>
+          <t>चेनाब</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>सिंधु</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>अणावली</t>
+          <t>रावी</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>स्वातंत्र्योत्तर भारत में सबसे अधिक संख्या में हड़पायुगीन स्थलों की खोज किस प्रांत में हुई है?</t>
+          <t>सिंधु घाटी सभ्यता को खोज निकालने में जिन दो भारतीय का नाम जुड़ा है</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>दयाराम साहनी एवं राखालदास बनर्जी</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>राजस्थान</t>
+          <t>जान मार्शल एवं ईश्वरी प्रसाद</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>पंजाब और हरियाणा</t>
+          <t>आशीर्वादीलाल श्रीवास्तव एवं रंगनाथ राव</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>उत्तर-पश्चिमी उत्तर प्रदेश</t>
+          <t>माधोस्वरूप वत्स एवं वी० बी० राव</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा एवं मोहनजोदड़ो की पुरातात्विक खुदाई के प्रभारी थे</t>
+          <t>हड़प्पाकालीन लोगों ने नगरों में घरों के विन्यास के लिए कौन-सी पद्धति अपनायी - थी ?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>सर जान मार्शल</t>
+          <t>ग्रीड पद्धति में</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>कर्नल टाड</t>
+          <t>त्रिभुजाकार आकृति में</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>लाई क्लाइव</t>
+          <t>गोलाकार आकृति में</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>लाई मैकाले</t>
+          <t>कमल पुष्प की आकृति का</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>सिंधु घाटी की सभ्यता में घोड़े के अवशेष कहाँ मिले हैं ?</t>
+          <t>हड़प्पा के मिट्टी के बर्तनों पर सामान्यतः किस रंग का उपयोग हुआ था?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>सुरकोटदा</t>
+          <t>लाल</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>वणावली</t>
+          <t>नीला-हरा</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>पांडु</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>नीला</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>किस पशु के अवशेष सिंधु घाटी सभ्यता में प्राप्त नहीं हुए हैं</t>
+          <t xml:space="preserve">	सिंधु सभ्यता में वृहत् स्नानागार पाया गया है</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>शेर</t>
+          <t>मोहनजोदड़ो में</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>घोड़ा</t>
+          <t>हड़प्पा में</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>गाय</t>
+          <t>लोथल में</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>हाथी</t>
+          <t>कालीबंगा में</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>निम्नलिखित विद्वानों में से हड़प्पा सभ्यता का सर्वप्रथम खोजकर्ता कौन था ?</t>
+          <t>निम्न में से किस पशु की आकृति जो मुहर पर मिली है, जिससे ज्ञात होता है, कि सिंधु घाटी एवं मेसोपोटामिया की सभ्यताओं के मध्य व्यापारिक संबंध थे</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>दयाराम सहनी</t>
+          <t>बैल</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>सर जॉन मार्शल</t>
+          <t>गधा</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>आर० डी० बनर्जी</t>
+          <t>हाथी</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ए० कनिंघम</t>
+          <t>घोड़ा</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता के घर किससे बनाए जाते थे ?</t>
+          <t xml:space="preserve">	हड़प्पा के काल का ताँबे का रथ किस स्थान से प्राप्त हुआ है ?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ईंट से</t>
+          <t>दैमावाद</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>बांस से</t>
+          <t>बणावली</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>पत्थर से</t>
+          <t>कुणाल</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>लकड़ी से</t>
+          <t>राखीगढ़ी</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>सिंधु घाटी सभ्यता को खोज निकालने में जिन दो भारतीय का नाम जुड़ा है</t>
+          <t xml:space="preserve">	सिंधु घाटी सभ्यता जानी जाती है।</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>दयाराम साहनी एवं राखालदास बनर्जी</t>
+          <t>अपने नगर नियोजन के लिए</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>जान मार्शल एवं ईश्वरी प्रसाद</t>
+          <t>मोहनजोदड़ो एवं हड़प्पा के लिए</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>आशीर्वादीलाल श्रीवास्तव एवं रंगनाथ राव</t>
+          <t>अपने कृषि संबंधी कार्यों के लिए</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>माधोस्वरूप वत्स एवं वी० बी० राव</t>
+          <t>अपने उद्योगों के लिए</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>कौन-कौन से नगर सिंधु सभ्यता के बंदरगाह नगर थे ?</t>
+          <t>हड़प्पावासी लाजवर्द-Lapislazuli- (भवन निर्माण की सामग्री) का आयात कहाँ से करते थे ?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>इनमें से सभी</t>
+          <t>हिन्दूकुश क्षेत्र के बदख्शा से</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>कुनतासी</t>
+          <t>ईरान से</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>अल्लाहदिनो एवं बालाकोट</t>
+          <t>दक्षिण भारत से</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>लोथल एवं सुत्कागेंडर</t>
+          <t>बलूचिस्तान से</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">	निम्नलिखित में से कौन-सी फसल हड़प्पाकालीन लोगों द्वारा उत्पादित नहीं की जाती थी?</t>
+          <t>मोहनजोदड़ो को किस एक अन्य नाम से भी जाना जाता है ?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>दालें</t>
+          <t>मृतकों का टीला (Mound of Dead)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>चावल</t>
+          <t>दासों का टीला (Mound of Slaves)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>गेहूँ</t>
+          <t>कंकालों का टीला (Mound of Skeletons)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>जौ</t>
+          <t>जीवितों का टीला (Mound of Living)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">	निम्नलिखित में से किस हड़प्पाकालीन स्थल से युगल शवाधान का साक्ष्य मिला है</t>
+          <t>निम्नलिखित विद्वानों में से हड़प्पा सभ्यता का सर्वप्रथम खोजकर्ता कौन था ?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>दयाराम सहनी</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>सर जॉन मार्शल</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>बणावली</t>
+          <t>आर० डी० बनर्जी</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>ए० कनिंघम</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>सिंधु घाटी की सभ्यता निम्नलिखित में से किस सभ्यता के समकालीन नहीं थी ?</t>
+          <t xml:space="preserve">	हड़प्पा में एक उन्नत जल-प्रबंधन प्रणाली का पता चलता है</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ग्रीक की सभ्यता</t>
+          <t>धौलावीरा में</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>मेसोपोटामिया की सभ्यता</t>
+          <t>कालीबंगन में</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>चीन की सभ्यता</t>
+          <t>आलमगीरपुर में</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>मिस्र की सभ्यता</t>
+          <t>लोथल में</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>हड़प्पा के लोगों की सामाजिक पद्धति...... थी</t>
+          <t>चन्हुदड़ो के उत्खनन का निर्देशन किया था -</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>उचित समतावादी</t>
+          <t>जे. एच. मैके ने</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>दास-श्रमिक आधारित</t>
+          <t>सर जॉन मार्शल ने</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>वर्ण आधारित</t>
+          <t>आर. ई. एम. व्हीलर ने</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>जाति आधारित</t>
+          <t>सर ऑरेल स्टीन ने</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">	सूची-I को सूची-II से सुमेलित कीजिए : सूची-I A. सिंधु सभ्यता की उत्तरी सीमा B. सिंधु सभ्यता की दक्षिणी सीमा C. सिंधु सभ्यता की पूर्वी सीमा D. सिंधु सभ्यता की पश्चिमी सीमा सूची-II 1. माडा/जम्मू 2. दैमाबाद/महाराष्ट्र 3. आलमगीरपुर / उत्तर प्रदेश 4. सुत्कागेंडर/बलूचिस्तान</t>
+          <t>सिंधु घाटी सभ्यता की विकसित अवस्था में निम्नलिखित में से किस स्थल में घरों में कुँओं के अवशेष मिले हैं?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 3, D → 4</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A → 2, B → 1, C → 4, D → 3</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>A → 4, B → 3, C → 2, D → 1</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 4, D → 3</t>
+          <t>हडपा</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता के सम्पूर्ण क्षेत्र का आकार किस प्रकार का था ?</t>
+          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (स्थल) A. हड़प्पा B. मोहनजोदड़ो C. लोथल D. कालीबंगा सूची-II (नदी) 1. रावी 2. सिंधु 3. भोगवा 4. घग्घर</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>त्रिभुजाकार</t>
+          <t>A → 1, B → 2, C → 3, D → 4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>गोलाकार</t>
+          <t>A → 2, B → 1, C → 4, D → 3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>आयताकार</t>
+          <t>A → 4, B → 3, C → 2, D → 1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>वर्गाकार</t>
+          <t>A → 1, B → 2, C → 4, D → 3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">	सिंधु घाटी सभ्यता जानी जाती है।</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>अपने नगर नियोजन के लिए</t>
-        </is>
+          <t>निम्न में से कौन से लक्षण सभ्यता के लोगों का सही चित्रण करता हैं 1. उनके विशाल महल और मन्दिर होते थे 2. वे देवियों और देवताओं दोनों की पूजा करते थे l 3. वे युद्ध में घोड़ों द्वारा खींचे जानेवाले रथों का प्रयोग करते थे नीचे दिए गये कूट का प्रयोग कर सही कथन को चुनिए</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो एवं हड़प्पा के लिए</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>अपने कृषि संबंधी कार्यों के लिए</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>अपने उद्योगों के लिए</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>सिंधु घाटी स्थल कालीबंगन किस प्रदेश में है ?</t>
+          <t>निम्नलिखित में से कौन मोहनजोदड़ो की सबसे बड़ी इमारत मानी जाती है?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>राजस्थान में</t>
+          <t>विशाल अन्नागार / धान्यकोठार</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>गुजरात में</t>
+          <t>विशाल स्नानागार</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>मध्य प्रदेश में</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश में</t>
+          <t>सभा भवन</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता की खोज किस वर्ष में हुई थी ?</t>
+          <t xml:space="preserve">	हड़प्पा सभ्यता किस युग की थी ?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1921 ई०</t>
+          <t>कांस्य युग</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1901 ई०</t>
+          <t>नवपाषाण युग</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1942 ई०</t>
+          <t>पुरापाषाण युग</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1935 ई०</t>
+          <t>लौह युग</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता के बारे में कौन-सा कथन असत्य है?</t>
+          <t>सिंध का नखलिस्तान / बाग' हड़प्पा सभ्यता के किस पुरास्थल को कहा गया?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>लोग लोहे से परिचित थे</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>मातृदेवी की उपासना की जाती थी</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>व्यापार और वाणिज्य उन्नत दशा में था</t>
+          <t>कालीबंगा</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>नगरों में नालियों की सुदृढ़ व्यवस्था थी</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता का पत्तननगर (बंदरगाह) कौन-सा था ?</t>
+          <t>सिंधु सभ्यता के घर किससे बनाए जाते थे ?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>ईंट से</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>रोपड़</t>
+          <t>बांस से</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>पत्थर से</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>कालीबंगन</t>
+          <t>लकड़ी से</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता का कौन-सा स्थान भारत में स्थित है?</t>
+          <t xml:space="preserve">	हड़प्पा सभ्यता की खोज किस वर्ष में हुई थी ?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>1921 ई०</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>1935 ई०</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>1901 ई०</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>1942 ई०</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>कथन (A) ; हड़प्पा तथा मोहनजोदड़ों अय विलुप्त हो गए हैं। कारण (R) : वे उत्खनन के दौरान प्रकट हुए थे।</t>
+          <t>सिंधु सभ्यता का पत्तननगर (बंदरगाह) कौन-सा था ?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>A और R दोनों सही हैं तथा R, A का सही स्पष्टीकरण है</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>A और R दोनों सही हैं किन्तु R, A का सही स्पष्टीकरण नहीं है</t>
+          <t>रोपड़</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>A सही है किन्तु R गलत है</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>A गलत है किन्तु R सही है</t>
+          <t>कालीबंगन</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>हड़प्पाकालीन स्थल रोपड़/ पंजाव किस नदी के किनारे स्थित था ?</t>
+          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (प्राचीन स्थल) A. लोथल B. कालीबंगन C. धौलावीर D. बनवाली सूची-II (पुरातत्वीय अवशेष) 1. जूता हुआ खेत 2. गोदीबाड़ा (Dockyaard) 3. पकी मिट्टी की बनी हुई हल की प्रतिकृति 4. हड़प्पाई लिपि के बड़े आकार के दस चिन्हों वाला एक शिलालेख</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>सतलज</t>
+          <t>A → 2, B → 1, C → 4, D → 3</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>चेनाब</t>
+          <t>A → 3, B → 1, C → 4, D → 2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>सिंधु</t>
+          <t>A → 1, B → 2, C → 4, D → 3</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>रावी</t>
+          <t>A → 1, B → 2, C → 3, D → 4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>सिन्धु सभ्यता निम्नलिखित में से किस युग में पड़ता है?</t>
+          <t>किस हड़प्पाकालीन स्थल से प्राप्त जार पर चोंच में मछली दबाए चिड़िया एवं पेड़ के नीचे खड़ी लोमड़ी का चित्रांकन मिलता है, जो 'पंचतंत्र ' के लोमड़ी की कहानी सदृश्य है ?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>आद्य ऐतिहासिक काल (Proto-Historical Period)</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>उत्तर-प्रागैतिहासिक काल (Post-Historical Period)</t>
+          <t>रंगपुर</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>प्रागतिहासिक काल (Pre-Historical Period)</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ऐतिहासिक काल (Historical Period)</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता का सर्वाधिक उपयुक्त नाम क्या है?</t>
+          <t>कथन (A) ; हड़प्पा तथा मोहनजोदड़ों अय विलुप्त हो गए हैं। कारण (R) : वे उत्खनन के दौरान प्रकट हुए थे।</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता</t>
+          <t>A और R दोनों सही हैं तथा R, A का सही स्पष्टीकरण है</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता</t>
+          <t>A और R दोनों सही हैं किन्तु R, A का सही स्पष्टीकरण नहीं है</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>सिंधु घाटी सभ्यता</t>
+          <t>A सही है किन्तु R गलत है</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>A गलत है किन्तु R सही है</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (हडप्पीय स्थल) A. मांडा B. दायमाबाद C. कालीबंगा D. राखीगढ़ी सूची-II (स्थिति) 1. राजस्थान 2. हरियाणा 3. जम्मू-कश्मीर 4. महाराष्ट्र</t>
+          <t>हड़प्पा सभ्यता के बारे में कौन-सी उक्ति सही है ?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A → 3, B → 4, C → 1, D → 2</t>
+          <t>उन्होंने पशुपति का सम्मान करना आरंभ किया</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>A → 4, B → 1, C → 2, D → 3</t>
+          <t>उनकी संस्कृति सामान्यतः स्थिर नहीं थी।</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>A → 2, B → 3, C → 4, D → 1</t>
+          <t>गाय उनके लिए पवित्र थी</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 3, D → 4</t>
+          <t>उन्हें अश्वमेध का जानकारी थी</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>कपास का उत्पादन सर्वप्रथम सिन्धु क्षेत्र में हुआ, जिसे ग्रीक या यूनान के लोग किस नाम से पुकारा ?</t>
+          <t>निम्नलिखित में कौन-सा सिंधु स्थल समुद्र तट पर स्थित नहीं था ?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>सिन्डन (Sindon)</t>
+          <t>कोटदीजी</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>बालाकोट</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>a' एवं 'b' दोनों</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>कॉटन (Cotton)</t>
+          <t>सुरकोटदा</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो को किस एक अन्य नाम से भी जाना जाता है ?</t>
+          <t>स्वातंत्र्योत्तर भारत में सबसे अधिक संख्या में हड़पायुगीन स्थलों की खोज किस प्रांत में हुई है?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>मृतकों का टीला (Mound of Dead)</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>दासों का टीला (Mound of Slaves)</t>
+          <t>राजस्थान</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>कंकालों का टीला (Mound of Skeletons)</t>
+          <t>पंजाब और हरियाणा</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>जीवितों का टीला (Mound of Living)</t>
+          <t>उत्तर-पश्चिमी उत्तर प्रदेश</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>सिंधु घाटी सभ्यता के लोगों का मुख्य व्यवसाय क्या था ?</t>
+          <t>सिंधु सभ्यता का कौन-सा स्थान भारत में स्थित है?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>व्यापार</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>पशुपालन</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>शिकार</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>कृषि</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>सूची-I को सूची-II से सुमेलित कीजिए : सूची-I (प्राचीन स्थल) A. लोथल B. कालीबंगन C. धौलावीर D. बनवाली सूची-II (पुरातत्वीय अवशेष) 1. जूता हुआ खेत 2. गोदीबाड़ा (Dockyaard) 3. पकी मिट्टी की बनी हुई हल की प्रतिकृति 4. हड़प्पाई लिपि के बड़े आकार के दस चिन्हों वाला एक शिलालेख</t>
+          <t>सिन्धु सभ्यता निम्नलिखित में से किस युग में पड़ता है?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>A → 2, B → 1, C → 4, D → 3</t>
+          <t>आद्य ऐतिहासिक काल (Proto-Historical Period)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>A → 3, B → 1, C → 4, D → 2</t>
+          <t>उत्तर-प्रागैतिहासिक काल (Post-Historical Period)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 4, D → 3</t>
+          <t>प्रागतिहासिक काल (Pre-Historical Period)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>A → 1, B → 2, C → 3, D → 4</t>
+          <t>ऐतिहासिक काल (Historical Period)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता का सर्वाधिक मान्यता प्राप्त काल है</t>
+          <t xml:space="preserve">	सूची-I को सूची-II से सुमेलित कीजिए : सूची-I A. सिंधु सभ्यता की उत्तरी सीमा B. सिंधु सभ्यता की दक्षिणी सीमा C. सिंधु सभ्यता की पूर्वी सीमा D. सिंधु सभ्यता की पश्चिमी सीमा सूची-II 1. माडा/जम्मू 2. दैमाबाद/महाराष्ट्र 3. आलमगीरपुर / उत्तर प्रदेश 4. सुत्कागेंडर/बलूचिस्तान</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2500 ई०पू०-1750 ई०पू०</t>
+          <t>A → 1, B → 2, C → 3, D → 4</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2800 ई०पू०-2000 ई०पू०</t>
+          <t>A → 2, B → 1, C → 4, D → 3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>3500 ई०पू०-1800 ई०पू०</t>
+          <t>A → 4, B → 3, C → 2, D → 1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>निश्चित नहीं हो सका है</t>
+          <t>A → 1, B → 2, C → 4, D → 3</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता का प्रचलित नाम है।</t>
+          <t>हड़प्पावासी किन-किन धातुओं का आयात करते थे ? उत्तर कूट में दें - कूट : 1. चाँदी 2. टिन 3. सोना</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो की सभ्यता</t>
+          <t>1, 2 एवं 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>सिन्धु घाटी की सभ्यता</t>
+          <t>1 एवं 2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>लोथल सभ्यता</t>
+          <t>1 एवं 3</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता</t>
+          <t>2 एवं 3</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>अफगानिस्तान स्थित सिंधु सभ्यता के स्थल हैं</t>
+          <t>कौन-कौन से नगर सिंधु सभ्यता के बंदरगाह नगर थे ?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>(a) और (b) दोनों</t>
+          <t>इनमें से सभी</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>कुनतासी</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>सुर्तागोई</t>
+          <t>अल्लाहदिनो एवं बालाकोट</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>मुंडीगाक</t>
+          <t>लोथल एवं सुत्कागेंडर</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>सिंधु घाटी सभ्यता की विकसित अवस्था में निम्नलिखित में से किस स्थल में घरों में कुँओं के अवशेष मिले हैं?</t>
+          <t>सिंधु सभ्यता के बारे में कौन-सा कथन असत्य है?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>लोग लोहे से परिचित थे</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>मातृदेवी की उपासना की जाती थी</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>व्यापार और वाणिज्य उन्नत दशा में था</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>हडपा</t>
+          <t>नगरों में नालियों की सुदृढ़ व्यवस्था थी</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>सैंधव स्थलों के उत्खनन से प्राप्त मुहरों पर निम्नलिखित में से किस पशु का सर्वाधिक उत्कीर्णन हुआ है ?</t>
+          <t>हड़प्पा के लोगों की सामाजिक पद्धति...... थी</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>बैल</t>
+          <t>उचित समतावादी</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>हाथी</t>
+          <t>दास-श्रमिक आधारित</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>घोड़ा</t>
+          <t>वर्ण आधारित</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>शेर</t>
+          <t>जाति आधारित</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>भारत में खोजा गया सबसे पहला पुराना शहर था</t>
+          <t>हड़प्पा सभ्यता के सम्पूर्ण क्षेत्र का आकार किस प्रकार का था ?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>त्रिभुजाकार</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>गोलाकार</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>आयताकार</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>सिंध</t>
+          <t>वर्गाकार</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पा सभ्यता किस युग की थी ?</t>
+          <t xml:space="preserve">	मोहनजोदड़ो कहाँ स्थित है?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>कांस्य युग</t>
+          <t>सिंध</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>नवपाषाण युग</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>पुरापाषाण युग</t>
+          <t>उत्तर प्रदेश</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>लौह युग</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">	हड़प्पाकालीन समाज किन वर्गों में विभक्त था ?</t>
+          <t>किस पशु के अवशेष सिंधु घाटी सभ्यता में प्राप्त नहीं हुए हैं</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>विद्वान, योद्धा, व्यापारी और श्रमिक</t>
+          <t>शेर</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>शिकारी, पुजारी, किसान और क्षत्रिय</t>
+          <t>घोड़ा</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ब्राह्मण, क्षत्रिय, वैश्य और शूद्र</t>
+          <t>गाय</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>राजा, पुरोहित, सैनिक और शूद्र</t>
+          <t>हाथी</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>हड़प्पा सभ्यता के निवासी थे</t>
+          <t>सिंधु घाटी सभ्यता के लोगों का मुख्य व्यवसाय क्या था ?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>शहरी</t>
+          <t>व्यापार</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ग्रामीण</t>
+          <t>पशुपालन</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>यायावर / खानाबदोश</t>
+          <t>शिकार</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>जनजातीय</t>
+          <t>कृषि</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>निम्नलिखित में से कौन-सा हड़प्पाकालीन स्थल गुजरात में था ?</t>
+          <t>भारत में खोजा गया सबसे पहला पुराना शहर था</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>वणावली</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>रोपड़</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>सिंध</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>किस सिंधुकालीन स्थल से एक ईट पर बिल्ली का पीछा करते हुए कुत्ते के पंजों के निशान मिले हैं ?</t>
+          <t xml:space="preserve">	रंगपुर जहाँ हड़प्पा की समकालीन सभ्यता थी, है -</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>चन्हुदड़ो</t>
+          <t>सौराष्ट्र में</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>लोथल</t>
+          <t>राजस्थान में</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>उत्तर प्रदेश में</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>हड़प्पा</t>
+          <t>पंजाब में</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>सिंधु घाटी के लोग विश्वास करते थे</t>
+          <t xml:space="preserve">	सिंधु घाटी की सभ्यता कहाँ तक विस्तृत थी?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>मातृशक्ति में</t>
+          <t>पंजाब, राजस्थान, गुजरात, उत्तर प्रदेश, हरियाणा, सिंध और बलुचिस्तान</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>यज्ञ प्रणाली में</t>
+          <t>जाब, राजस्थान, गुजरात, उड़ीसा और बंगाल</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>कर्मकाण्ड में</t>
+          <t>राजस्थान, बिहार, बंगाल और उड़ीसा</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>आत्मा और ब्रह्म में</t>
+          <t>पंजाब, दिल्ली और जम्मू-कश्मीर</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>सैंधव सभ्यता की ईटों का अलंकरण किस स्थान से मिला है?</t>
+          <t>किस हड़प्पाकालीन स्थल से ‘पुजारी की प्रस्तर मूर्ति प्राप्त हुई है?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>कालीबंगा</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>चन्हूदड़ो</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो</t>
+          <t>रंगपुर</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>बणावली</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>हड़प्पा के मिट्टी के बर्तनों पर सामान्यतः किस रंग का उपयोग हुआ था?</t>
+          <t>हड़प्पा सभ्यता का सर्वाधिक मान्यता प्राप्त काल है</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>लाल</t>
+          <t>2500 ई०पू०-1750 ई०पू०</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>नीला-हरा</t>
+          <t>2800 ई०पू०-2000 ई०पू०</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>पांडु</t>
+          <t>3500 ई०पू०-1800 ई०पू०</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>नीला</t>
+          <t>निश्चित नहीं हो सका है</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">	रंगपुर जहाँ हड़प्पा की समकालीन सभ्यता थी, है -</t>
+          <t>किस सिंधुकालीन स्थल से एक ईट पर बिल्ली का पीछा करते हुए कुत्ते के पंजों के निशान मिले हैं ?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>सौराष्ट्र में</t>
+          <t>चन्हुदड़ो</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>राजस्थान में</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश में</t>
+          <t>मोहनजोदड़ो</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>पंजाब में</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>मोहनजोदड़ो से प्राप्त पशुपति शिव/ आद्य शिव मुहर में किन किन जानवरों का अंकन हुआ है ?</t>
+          <t>सिंधु घाटी स्थल कालीबंगन किस प्रदेश में है ?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>इनमें से सभी</t>
+          <t>राजस्थान में</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>हिरण</t>
+          <t>गुजरात में</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>गैंडा एवं भैंसा</t>
+          <t>मध्य प्रदेश में</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>व्याघ्र एवं हाथी</t>
+          <t>उत्तर प्रदेश में</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>सिंधु सभ्यता की मुद्रा में किस देवता के रामतुल्य चित्रांकन मिलता है</t>
+          <t xml:space="preserve">	हड़प्पावासी किस धातु से परिचित नहीं थे ?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>आद्य शिव</t>
+          <t>लोहा</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>आद्य ब्रह्मा</t>
+          <t>टीन एवं सीसा</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>अद्य विष्णु</t>
+          <t>तांबा एवं कांसा</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>आद्य इन्द्र</t>
+          <t>सोना एवं चांदी</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>हड़प्पाकालीन स्थलों में अभी तक किस धातु की प्राप्ति नहीं हुई है ?</t>
+          <t>पैमानों की खोज ने यह सिद्ध कर दिया है कि सिंधु घाटी के लोग माप और तौल से परिचित थे। यह खोज कहाँ पर हुई ?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>लोहा</t>
+          <t>लोथल</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>चांदी</t>
+          <t>कालीबंगन</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>स्वर्ण</t>
+          <t>हड़प्पा</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>तांबा</t>
+          <t>चहुदड़ी</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>मांडा किस नदी के किनारे स्थित था?</t>
+          <t>हड़प्पा सभ्यता का प्रचलित नाम है।</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>चेनाब</t>
+          <t>मोहनजोदड़ो की सभ्यता</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>सतलज</t>
+          <t>सिन्धु घाटी की सभ्यता</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>रावी</t>
+          <t>लोथल सभ्यता</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>सिंधु</t>
+          <t>सिंधु सभ्यता</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
